--- a/output/MLB_2026_Predictions.xlsx
+++ b/output/MLB_2026_Predictions.xlsx
@@ -569,7 +569,9 @@
       <c r="B2" t="n">
         <v>0.195</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0.206</v>
+      </c>
       <c r="D2" t="n">
         <v>111</v>
       </c>
@@ -581,7 +583,9 @@
       <c r="H2" t="n">
         <v>54</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
       <c r="J2" t="n">
         <v>129</v>
       </c>
@@ -616,7 +620,9 @@
       <c r="B3" t="n">
         <v>0.331</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0.291</v>
+      </c>
       <c r="D3" t="n">
         <v>119</v>
       </c>
@@ -628,7 +634,9 @@
       <c r="H3" t="n">
         <v>53</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
       <c r="J3" t="n">
         <v>110</v>
       </c>
@@ -663,7 +671,9 @@
       <c r="B4" t="n">
         <v>0.301</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0.276</v>
+      </c>
       <c r="D4" t="n">
         <v>120</v>
       </c>
@@ -675,7 +685,9 @@
       <c r="H4" t="n">
         <v>51</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>46</v>
+      </c>
       <c r="J4" t="n">
         <v>114</v>
       </c>
@@ -710,7 +722,9 @@
       <c r="B5" t="n">
         <v>0.22</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0.217</v>
+      </c>
       <c r="D5" t="n">
         <v>89</v>
       </c>
@@ -722,7 +736,9 @@
       <c r="H5" t="n">
         <v>50</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>42</v>
+      </c>
       <c r="J5" t="n">
         <v>99</v>
       </c>
@@ -757,7 +773,9 @@
       <c r="B6" t="n">
         <v>0.28</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D6" t="n">
         <v>107</v>
       </c>
@@ -769,7 +787,9 @@
       <c r="H6" t="n">
         <v>44</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>41</v>
+      </c>
       <c r="J6" t="n">
         <v>129</v>
       </c>
@@ -804,7 +824,9 @@
       <c r="B7" t="n">
         <v>0.246</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D7" t="n">
         <v>96</v>
       </c>
@@ -816,7 +838,9 @@
       <c r="H7" t="n">
         <v>41</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>40</v>
+      </c>
       <c r="J7" t="n">
         <v>126</v>
       </c>
@@ -851,7 +875,9 @@
       <c r="B8" t="n">
         <v>0.318</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>0.276</v>
+      </c>
       <c r="D8" t="n">
         <v>139</v>
       </c>
@@ -863,7 +889,9 @@
       <c r="H8" t="n">
         <v>38</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>48</v>
+      </c>
       <c r="J8" t="n">
         <v>120</v>
       </c>
@@ -898,7 +926,9 @@
       <c r="B9" t="n">
         <v>0.294</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D9" t="n">
         <v>94</v>
       </c>
@@ -910,7 +940,9 @@
       <c r="H9" t="n">
         <v>37</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>38</v>
+      </c>
       <c r="J9" t="n">
         <v>104</v>
       </c>
@@ -945,7 +977,9 @@
       <c r="B10" t="n">
         <v>0.27</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>0.249</v>
+      </c>
       <c r="D10" t="n">
         <v>99</v>
       </c>
@@ -957,7 +991,9 @@
       <c r="H10" t="n">
         <v>37</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>37</v>
+      </c>
       <c r="J10" t="n">
         <v>112</v>
       </c>
@@ -992,7 +1028,9 @@
       <c r="B11" t="n">
         <v>0.331</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>0.331</v>
+      </c>
       <c r="D11" t="n">
         <v>125</v>
       </c>
@@ -1004,7 +1042,9 @@
       <c r="H11" t="n">
         <v>36</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>34</v>
+      </c>
       <c r="J11" t="n">
         <v>113</v>
       </c>
@@ -1039,7 +1079,9 @@
       <c r="B12" t="n">
         <v>0.292</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D12" t="n">
         <v>95</v>
       </c>
@@ -1051,7 +1093,9 @@
       <c r="H12" t="n">
         <v>34</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>30</v>
+      </c>
       <c r="J12" t="n">
         <v>102</v>
       </c>
@@ -1086,7 +1130,9 @@
       <c r="B13" t="n">
         <v>0.317</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>0.29</v>
+      </c>
       <c r="D13" t="n">
         <v>109</v>
       </c>
@@ -1098,7 +1144,9 @@
       <c r="H13" t="n">
         <v>33</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>30</v>
+      </c>
       <c r="J13" t="n">
         <v>98</v>
       </c>
@@ -1133,7 +1181,9 @@
       <c r="B14" t="n">
         <v>0.201</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D14" t="n">
         <v>47</v>
       </c>
@@ -1145,7 +1195,9 @@
       <c r="H14" t="n">
         <v>32</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>28</v>
+      </c>
       <c r="J14" t="n">
         <v>61</v>
       </c>
@@ -1180,7 +1232,9 @@
       <c r="B15" t="n">
         <v>0.203</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>0.213</v>
+      </c>
       <c r="D15" t="n">
         <v>66</v>
       </c>
@@ -1192,7 +1246,9 @@
       <c r="H15" t="n">
         <v>32</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>33</v>
+      </c>
       <c r="J15" t="n">
         <v>93</v>
       </c>
@@ -1227,7 +1283,9 @@
       <c r="B16" t="n">
         <v>0.254</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D16" t="n">
         <v>86</v>
       </c>
@@ -1239,7 +1297,9 @@
       <c r="H16" t="n">
         <v>32</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>37</v>
+      </c>
       <c r="J16" t="n">
         <v>114</v>
       </c>
@@ -1274,7 +1334,9 @@
       <c r="B17" t="n">
         <v>0.305</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.312</v>
+      </c>
       <c r="D17" t="n">
         <v>103</v>
       </c>
@@ -1286,7 +1348,9 @@
       <c r="H17" t="n">
         <v>31</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>30</v>
+      </c>
       <c r="J17" t="n">
         <v>97</v>
       </c>
@@ -1321,7 +1385,9 @@
       <c r="B18" t="n">
         <v>0.303</v>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>0.277</v>
+      </c>
       <c r="D18" t="n">
         <v>110</v>
       </c>
@@ -1333,7 +1399,9 @@
       <c r="H18" t="n">
         <v>31</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>31</v>
+      </c>
       <c r="J18" t="n">
         <v>92</v>
       </c>
@@ -1368,7 +1436,9 @@
       <c r="B19" t="n">
         <v>0.252</v>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>0.272</v>
+      </c>
       <c r="D19" t="n">
         <v>94</v>
       </c>
@@ -1380,7 +1450,9 @@
       <c r="H19" t="n">
         <v>30</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>27</v>
+      </c>
       <c r="J19" t="n">
         <v>96</v>
       </c>
@@ -1415,7 +1487,9 @@
       <c r="B20" t="n">
         <v>0.255</v>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D20" t="n">
         <v>78</v>
       </c>
@@ -1427,7 +1501,9 @@
       <c r="H20" t="n">
         <v>30</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
       <c r="J20" t="n">
         <v>92</v>
       </c>
@@ -1462,7 +1538,9 @@
       <c r="B21" t="n">
         <v>0.231</v>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D21" t="n">
         <v>60</v>
       </c>
@@ -1474,7 +1552,9 @@
       <c r="H21" t="n">
         <v>29</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>21</v>
+      </c>
       <c r="J21" t="n">
         <v>61</v>
       </c>
@@ -1509,7 +1589,9 @@
       <c r="B22" t="n">
         <v>0.249</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D22" t="n">
         <v>92</v>
       </c>
@@ -1521,7 +1603,9 @@
       <c r="H22" t="n">
         <v>29</v>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>26</v>
+      </c>
       <c r="J22" t="n">
         <v>98</v>
       </c>
@@ -1556,7 +1640,9 @@
       <c r="B23" t="n">
         <v>0.236</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D23" t="n">
         <v>61</v>
       </c>
@@ -1568,7 +1654,9 @@
       <c r="H23" t="n">
         <v>29</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>27</v>
+      </c>
       <c r="J23" t="n">
         <v>74</v>
       </c>
@@ -1603,7 +1691,9 @@
       <c r="B24" t="n">
         <v>0.295</v>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D24" t="n">
         <v>111</v>
       </c>
@@ -1615,7 +1705,9 @@
       <c r="H24" t="n">
         <v>29</v>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>29</v>
+      </c>
       <c r="J24" t="n">
         <v>99</v>
       </c>
@@ -1650,7 +1742,9 @@
       <c r="B25" t="n">
         <v>0.266</v>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>0.259</v>
+      </c>
       <c r="D25" t="n">
         <v>94</v>
       </c>
@@ -1662,7 +1756,9 @@
       <c r="H25" t="n">
         <v>29</v>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>33</v>
+      </c>
       <c r="J25" t="n">
         <v>97</v>
       </c>
@@ -1697,7 +1793,9 @@
       <c r="B26" t="n">
         <v>0.256</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.248</v>
+      </c>
       <c r="D26" t="n">
         <v>51</v>
       </c>
@@ -1709,7 +1807,9 @@
       <c r="H26" t="n">
         <v>29</v>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>27</v>
+      </c>
       <c r="J26" t="n">
         <v>104</v>
       </c>
@@ -1744,7 +1844,9 @@
       <c r="B27" t="n">
         <v>0.193</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D27" t="n">
         <v>59</v>
       </c>
@@ -1756,7 +1858,9 @@
       <c r="H27" t="n">
         <v>29</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>27</v>
+      </c>
       <c r="J27" t="n">
         <v>70</v>
       </c>
@@ -1791,7 +1895,9 @@
       <c r="B28" t="n">
         <v>0.299</v>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>0.292</v>
+      </c>
       <c r="D28" t="n">
         <v>114</v>
       </c>
@@ -1803,7 +1909,9 @@
       <c r="H28" t="n">
         <v>28</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>30</v>
+      </c>
       <c r="J28" t="n">
         <v>91</v>
       </c>
@@ -1838,7 +1946,9 @@
       <c r="B29" t="n">
         <v>0.226</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="n">
+        <v>0.222</v>
+      </c>
       <c r="D29" t="n">
         <v>72</v>
       </c>
@@ -1850,7 +1960,9 @@
       <c r="H29" t="n">
         <v>28</v>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>29</v>
+      </c>
       <c r="J29" t="n">
         <v>69</v>
       </c>
@@ -1885,7 +1997,9 @@
       <c r="B30" t="n">
         <v>0.282</v>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D30" t="n">
         <v>119</v>
       </c>
@@ -1897,7 +2011,9 @@
       <c r="H30" t="n">
         <v>28</v>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>30</v>
+      </c>
       <c r="J30" t="n">
         <v>87</v>
       </c>
@@ -1932,7 +2048,9 @@
       <c r="B31" t="n">
         <v>0.286</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.277</v>
+      </c>
       <c r="D31" t="n">
         <v>106</v>
       </c>
@@ -1944,7 +2062,9 @@
       <c r="H31" t="n">
         <v>28</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>31</v>
+      </c>
       <c r="J31" t="n">
         <v>109</v>
       </c>
@@ -1979,7 +2099,9 @@
       <c r="B32" t="n">
         <v>0.314</v>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>0.297</v>
+      </c>
       <c r="D32" t="n">
         <v>76</v>
       </c>
@@ -1991,7 +2113,9 @@
       <c r="H32" t="n">
         <v>27</v>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>26</v>
+      </c>
       <c r="J32" t="n">
         <v>84</v>
       </c>
@@ -2026,7 +2150,9 @@
       <c r="B33" t="n">
         <v>0.275</v>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>0.293</v>
+      </c>
       <c r="D33" t="n">
         <v>103</v>
       </c>
@@ -2038,7 +2164,9 @@
       <c r="H33" t="n">
         <v>27</v>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>30</v>
+      </c>
       <c r="J33" t="n">
         <v>92</v>
       </c>
@@ -2073,7 +2201,9 @@
       <c r="B34" t="n">
         <v>0.298</v>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>0.285</v>
+      </c>
       <c r="D34" t="n">
         <v>108</v>
       </c>
@@ -2085,7 +2215,9 @@
       <c r="H34" t="n">
         <v>27</v>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>24</v>
+      </c>
       <c r="J34" t="n">
         <v>96</v>
       </c>
@@ -2120,7 +2252,9 @@
       <c r="B35" t="n">
         <v>0.234</v>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D35" t="n">
         <v>70</v>
       </c>
@@ -2132,7 +2266,9 @@
       <c r="H35" t="n">
         <v>27</v>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>27</v>
+      </c>
       <c r="J35" t="n">
         <v>70</v>
       </c>
@@ -2167,7 +2303,9 @@
       <c r="B36" t="n">
         <v>0.22</v>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>0.223</v>
+      </c>
       <c r="D36" t="n">
         <v>100</v>
       </c>
@@ -2179,7 +2317,9 @@
       <c r="H36" t="n">
         <v>27</v>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>28</v>
+      </c>
       <c r="J36" t="n">
         <v>91</v>
       </c>
@@ -2214,7 +2354,9 @@
       <c r="B37" t="n">
         <v>0.263</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D37" t="n">
         <v>72</v>
       </c>
@@ -2226,7 +2368,9 @@
       <c r="H37" t="n">
         <v>26</v>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>28</v>
+      </c>
       <c r="J37" t="n">
         <v>87</v>
       </c>
@@ -2261,7 +2405,9 @@
       <c r="B38" t="n">
         <v>0.277</v>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D38" t="n">
         <v>85</v>
       </c>
@@ -2273,7 +2419,9 @@
       <c r="H38" t="n">
         <v>26</v>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>24</v>
+      </c>
       <c r="J38" t="n">
         <v>82</v>
       </c>
@@ -2308,7 +2456,9 @@
       <c r="B39" t="n">
         <v>0.275</v>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>0.272</v>
+      </c>
       <c r="D39" t="n">
         <v>68</v>
       </c>
@@ -2320,7 +2470,9 @@
       <c r="H39" t="n">
         <v>26</v>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>25</v>
+      </c>
       <c r="J39" t="n">
         <v>104</v>
       </c>
@@ -2355,7 +2507,9 @@
       <c r="B40" t="n">
         <v>0.218</v>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>0.226</v>
+      </c>
       <c r="D40" t="n">
         <v>61</v>
       </c>
@@ -2367,7 +2521,9 @@
       <c r="H40" t="n">
         <v>26</v>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>25</v>
+      </c>
       <c r="J40" t="n">
         <v>74</v>
       </c>
@@ -2402,7 +2558,9 @@
       <c r="B41" t="n">
         <v>0.267</v>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>0.254</v>
+      </c>
       <c r="D41" t="n">
         <v>77</v>
       </c>
@@ -2414,7 +2572,9 @@
       <c r="H41" t="n">
         <v>26</v>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>26</v>
+      </c>
       <c r="J41" t="n">
         <v>85</v>
       </c>
@@ -2449,7 +2609,9 @@
       <c r="B42" t="n">
         <v>0.234</v>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>0.249</v>
+      </c>
       <c r="D42" t="n">
         <v>63</v>
       </c>
@@ -2461,7 +2623,9 @@
       <c r="H42" t="n">
         <v>26</v>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>28</v>
+      </c>
       <c r="J42" t="n">
         <v>82</v>
       </c>
@@ -2496,7 +2660,9 @@
       <c r="B43" t="n">
         <v>0.254</v>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>0.256</v>
+      </c>
       <c r="D43" t="n">
         <v>82</v>
       </c>
@@ -2508,7 +2674,9 @@
       <c r="H43" t="n">
         <v>26</v>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>30</v>
+      </c>
       <c r="J43" t="n">
         <v>74</v>
       </c>
@@ -2543,7 +2711,9 @@
       <c r="B44" t="n">
         <v>0.29</v>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>0.269</v>
+      </c>
       <c r="D44" t="n">
         <v>84</v>
       </c>
@@ -2555,7 +2725,9 @@
       <c r="H44" t="n">
         <v>25</v>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>24</v>
+      </c>
       <c r="J44" t="n">
         <v>77</v>
       </c>
@@ -2590,7 +2762,9 @@
       <c r="B45" t="n">
         <v>0.243</v>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D45" t="n">
         <v>109</v>
       </c>
@@ -2602,7 +2776,9 @@
       <c r="H45" t="n">
         <v>25</v>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>29</v>
+      </c>
       <c r="J45" t="n">
         <v>65</v>
       </c>
@@ -2637,7 +2813,9 @@
       <c r="B46" t="n">
         <v>0.224</v>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>0.227</v>
+      </c>
       <c r="D46" t="n">
         <v>62</v>
       </c>
@@ -2649,7 +2827,9 @@
       <c r="H46" t="n">
         <v>25</v>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>19</v>
+      </c>
       <c r="J46" t="n">
         <v>73</v>
       </c>
@@ -2684,7 +2864,9 @@
       <c r="B47" t="n">
         <v>0.306</v>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>0.288</v>
+      </c>
       <c r="D47" t="n">
         <v>86</v>
       </c>
@@ -2696,7 +2878,9 @@
       <c r="H47" t="n">
         <v>25</v>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>24</v>
+      </c>
       <c r="J47" t="n">
         <v>79</v>
       </c>
@@ -2731,7 +2915,9 @@
       <c r="B48" t="n">
         <v>0.222</v>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D48" t="n">
         <v>88</v>
       </c>
@@ -2743,7 +2929,9 @@
       <c r="H48" t="n">
         <v>25</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>24</v>
+      </c>
       <c r="J48" t="n">
         <v>81</v>
       </c>
@@ -2778,7 +2966,9 @@
       <c r="B49" t="n">
         <v>0.28</v>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>0.301</v>
+      </c>
       <c r="D49" t="n">
         <v>97</v>
       </c>
@@ -2790,7 +2980,9 @@
       <c r="H49" t="n">
         <v>25</v>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>26</v>
+      </c>
       <c r="J49" t="n">
         <v>89</v>
       </c>
@@ -2825,7 +3017,9 @@
       <c r="B50" t="n">
         <v>0.225</v>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>0.246</v>
+      </c>
       <c r="D50" t="n">
         <v>66</v>
       </c>
@@ -2837,7 +3031,9 @@
       <c r="H50" t="n">
         <v>25</v>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>27</v>
+      </c>
       <c r="J50" t="n">
         <v>78</v>
       </c>
@@ -2872,7 +3068,9 @@
       <c r="B51" t="n">
         <v>0.228</v>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>0.222</v>
+      </c>
       <c r="D51" t="n">
         <v>67</v>
       </c>
@@ -2884,7 +3082,9 @@
       <c r="H51" t="n">
         <v>24</v>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>23</v>
+      </c>
       <c r="J51" t="n">
         <v>86</v>
       </c>
@@ -2919,7 +3119,9 @@
       <c r="B52" t="n">
         <v>0.252</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D52" t="n">
         <v>105</v>
       </c>
@@ -2931,7 +3133,9 @@
       <c r="H52" t="n">
         <v>24</v>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>26</v>
+      </c>
       <c r="J52" t="n">
         <v>80</v>
       </c>
@@ -2966,7 +3170,9 @@
       <c r="B53" t="n">
         <v>0.3</v>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>0.257</v>
+      </c>
       <c r="D53" t="n">
         <v>93</v>
       </c>
@@ -2978,7 +3184,9 @@
       <c r="H53" t="n">
         <v>24</v>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>21</v>
+      </c>
       <c r="J53" t="n">
         <v>77</v>
       </c>
@@ -3013,7 +3221,9 @@
       <c r="B54" t="n">
         <v>0.209</v>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>0.214</v>
+      </c>
       <c r="D54" t="n">
         <v>51</v>
       </c>
@@ -3025,7 +3235,9 @@
       <c r="H54" t="n">
         <v>24</v>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>24</v>
+      </c>
       <c r="J54" t="n">
         <v>70</v>
       </c>
@@ -3060,7 +3272,9 @@
       <c r="B55" t="n">
         <v>0.242</v>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>0.263</v>
+      </c>
       <c r="D55" t="n">
         <v>93</v>
       </c>
@@ -3072,7 +3286,9 @@
       <c r="H55" t="n">
         <v>24</v>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>26</v>
+      </c>
       <c r="J55" t="n">
         <v>82</v>
       </c>
@@ -3107,7 +3323,9 @@
       <c r="B56" t="n">
         <v>0.264</v>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D56" t="n">
         <v>85</v>
       </c>
@@ -3119,7 +3337,9 @@
       <c r="H56" t="n">
         <v>23</v>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>20</v>
+      </c>
       <c r="J56" t="n">
         <v>81</v>
       </c>
@@ -3154,7 +3374,9 @@
       <c r="B57" t="n">
         <v>0.285</v>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D57" t="n">
         <v>83</v>
       </c>
@@ -3166,7 +3388,9 @@
       <c r="H57" t="n">
         <v>23</v>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>22</v>
+      </c>
       <c r="J57" t="n">
         <v>84</v>
       </c>
@@ -3201,7 +3425,9 @@
       <c r="B58" t="n">
         <v>0.169</v>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>0.188</v>
+      </c>
       <c r="D58" t="n">
         <v>45</v>
       </c>
@@ -3213,7 +3439,9 @@
       <c r="H58" t="n">
         <v>23</v>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>19</v>
+      </c>
       <c r="J58" t="n">
         <v>51</v>
       </c>
@@ -3248,7 +3476,9 @@
       <c r="B59" t="n">
         <v>0.25</v>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>0.282</v>
+      </c>
       <c r="D59" t="n">
         <v>85</v>
       </c>
@@ -3260,7 +3490,9 @@
       <c r="H59" t="n">
         <v>23</v>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>18</v>
+      </c>
       <c r="J59" t="n">
         <v>69</v>
       </c>
@@ -3295,7 +3527,9 @@
       <c r="B60" t="n">
         <v>0.246</v>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>0.248</v>
+      </c>
       <c r="D60" t="n">
         <v>56</v>
       </c>
@@ -3307,7 +3541,9 @@
       <c r="H60" t="n">
         <v>23</v>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>20</v>
+      </c>
       <c r="J60" t="n">
         <v>58</v>
       </c>
@@ -3342,7 +3578,9 @@
       <c r="B61" t="n">
         <v>0.205</v>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>0.202</v>
+      </c>
       <c r="D61" t="n">
         <v>56</v>
       </c>
@@ -3354,7 +3592,9 @@
       <c r="H61" t="n">
         <v>23</v>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
       <c r="J61" t="n">
         <v>50</v>
       </c>
@@ -3389,7 +3629,9 @@
       <c r="B62" t="n">
         <v>0.233</v>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D62" t="n">
         <v>77</v>
       </c>
@@ -3401,7 +3643,9 @@
       <c r="H62" t="n">
         <v>23</v>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>24</v>
+      </c>
       <c r="J62" t="n">
         <v>70</v>
       </c>
@@ -3436,7 +3680,9 @@
       <c r="B63" t="n">
         <v>0.189</v>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>0.207</v>
+      </c>
       <c r="D63" t="n">
         <v>31</v>
       </c>
@@ -3448,7 +3694,9 @@
       <c r="H63" t="n">
         <v>23</v>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>25</v>
+      </c>
       <c r="J63" t="n">
         <v>62</v>
       </c>
@@ -3483,7 +3731,9 @@
       <c r="B64" t="n">
         <v>0.209</v>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>0.223</v>
+      </c>
       <c r="D64" t="n">
         <v>59</v>
       </c>
@@ -3495,7 +3745,9 @@
       <c r="H64" t="n">
         <v>23</v>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>23</v>
+      </c>
       <c r="J64" t="n">
         <v>68</v>
       </c>
@@ -3530,7 +3782,9 @@
       <c r="B65" t="n">
         <v>0.245</v>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>0.258</v>
+      </c>
       <c r="D65" t="n">
         <v>80</v>
       </c>
@@ -3542,7 +3796,9 @@
       <c r="H65" t="n">
         <v>23</v>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>23</v>
+      </c>
       <c r="J65" t="n">
         <v>95</v>
       </c>
@@ -3577,7 +3833,9 @@
       <c r="B66" t="n">
         <v>0.24</v>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D66" t="n">
         <v>60</v>
       </c>
@@ -3589,7 +3847,9 @@
       <c r="H66" t="n">
         <v>23</v>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>22</v>
+      </c>
       <c r="J66" t="n">
         <v>63</v>
       </c>
@@ -3624,7 +3884,9 @@
       <c r="B67" t="n">
         <v>0.241</v>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D67" t="n">
         <v>55</v>
       </c>
@@ -3636,7 +3898,9 @@
       <c r="H67" t="n">
         <v>23</v>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>24</v>
+      </c>
       <c r="J67" t="n">
         <v>71</v>
       </c>
@@ -3671,7 +3935,9 @@
       <c r="B68" t="n">
         <v>0.286</v>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>0.286</v>
+      </c>
       <c r="D68" t="n">
         <v>79</v>
       </c>
@@ -3683,7 +3949,9 @@
       <c r="H68" t="n">
         <v>22</v>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>22</v>
+      </c>
       <c r="J68" t="n">
         <v>80</v>
       </c>
@@ -3718,7 +3986,9 @@
       <c r="B69" t="n">
         <v>0.226</v>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="n">
+        <v>0.239</v>
+      </c>
       <c r="D69" t="n">
         <v>61</v>
       </c>
@@ -3730,7 +4000,9 @@
       <c r="H69" t="n">
         <v>22</v>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>26</v>
+      </c>
       <c r="J69" t="n">
         <v>77</v>
       </c>
@@ -3765,7 +4037,9 @@
       <c r="B70" t="n">
         <v>0.281</v>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="n">
+        <v>0.276</v>
+      </c>
       <c r="D70" t="n">
         <v>80</v>
       </c>
@@ -3777,7 +4051,9 @@
       <c r="H70" t="n">
         <v>22</v>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>22</v>
+      </c>
       <c r="J70" t="n">
         <v>76</v>
       </c>
@@ -3812,7 +4088,9 @@
       <c r="B71" t="n">
         <v>0.226</v>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>0.228</v>
+      </c>
       <c r="D71" t="n">
         <v>58</v>
       </c>
@@ -3824,7 +4102,9 @@
       <c r="H71" t="n">
         <v>22</v>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>22</v>
+      </c>
       <c r="J71" t="n">
         <v>69</v>
       </c>
@@ -3859,7 +4139,9 @@
       <c r="B72" t="n">
         <v>0.224</v>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D72" t="n">
         <v>91</v>
       </c>
@@ -3871,7 +4153,9 @@
       <c r="H72" t="n">
         <v>22</v>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>24</v>
+      </c>
       <c r="J72" t="n">
         <v>74</v>
       </c>
@@ -3906,7 +4190,9 @@
       <c r="B73" t="n">
         <v>0.266</v>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>0.213</v>
+      </c>
       <c r="D73" t="n">
         <v>44</v>
       </c>
@@ -3918,7 +4204,9 @@
       <c r="H73" t="n">
         <v>22</v>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>17</v>
+      </c>
       <c r="J73" t="n">
         <v>65</v>
       </c>
@@ -3953,7 +4241,9 @@
       <c r="B74" t="n">
         <v>0.248</v>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>0.245</v>
+      </c>
       <c r="D74" t="n">
         <v>46</v>
       </c>
@@ -3965,7 +4255,9 @@
       <c r="H74" t="n">
         <v>22</v>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>22</v>
+      </c>
       <c r="J74" t="n">
         <v>70</v>
       </c>
@@ -4000,7 +4292,9 @@
       <c r="B75" t="n">
         <v>0.315</v>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D75" t="n">
         <v>59</v>
       </c>
@@ -4012,7 +4306,9 @@
       <c r="H75" t="n">
         <v>21</v>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
       <c r="J75" t="n">
         <v>76</v>
       </c>
@@ -4047,7 +4343,9 @@
       <c r="B76" t="n">
         <v>0.242</v>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D76" t="n">
         <v>53</v>
       </c>
@@ -4059,7 +4357,9 @@
       <c r="H76" t="n">
         <v>21</v>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>25</v>
+      </c>
       <c r="J76" t="n">
         <v>76</v>
       </c>
@@ -4094,7 +4394,9 @@
       <c r="B77" t="n">
         <v>0.221</v>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="n">
+        <v>0.236</v>
+      </c>
       <c r="D77" t="n">
         <v>57</v>
       </c>
@@ -4106,7 +4408,9 @@
       <c r="H77" t="n">
         <v>21</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>22</v>
+      </c>
       <c r="J77" t="n">
         <v>71</v>
       </c>
@@ -4141,7 +4445,9 @@
       <c r="B78" t="n">
         <v>0.217</v>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>0.236</v>
+      </c>
       <c r="D78" t="n">
         <v>59</v>
       </c>
@@ -4153,7 +4459,9 @@
       <c r="H78" t="n">
         <v>21</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>17</v>
+      </c>
       <c r="J78" t="n">
         <v>68</v>
       </c>
@@ -4188,7 +4496,9 @@
       <c r="B79" t="n">
         <v>0.252</v>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>0.256</v>
+      </c>
       <c r="D79" t="n">
         <v>71</v>
       </c>
@@ -4200,7 +4510,9 @@
       <c r="H79" t="n">
         <v>21</v>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>22</v>
+      </c>
       <c r="J79" t="n">
         <v>69</v>
       </c>
@@ -4235,7 +4547,9 @@
       <c r="B80" t="n">
         <v>0.239</v>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="n">
+        <v>0.222</v>
+      </c>
       <c r="D80" t="n">
         <v>59</v>
       </c>
@@ -4247,7 +4561,9 @@
       <c r="H80" t="n">
         <v>21</v>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>19</v>
+      </c>
       <c r="J80" t="n">
         <v>63</v>
       </c>
@@ -4282,7 +4598,9 @@
       <c r="B81" t="n">
         <v>0.262</v>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>0.251</v>
+      </c>
       <c r="D81" t="n">
         <v>86</v>
       </c>
@@ -4294,7 +4612,9 @@
       <c r="H81" t="n">
         <v>21</v>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>21</v>
+      </c>
       <c r="J81" t="n">
         <v>58</v>
       </c>
@@ -4329,7 +4649,9 @@
       <c r="B82" t="n">
         <v>0.193</v>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D82" t="n">
         <v>55</v>
       </c>
@@ -4341,7 +4663,9 @@
       <c r="H82" t="n">
         <v>21</v>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>20</v>
+      </c>
       <c r="J82" t="n">
         <v>55</v>
       </c>
@@ -4376,7 +4700,9 @@
       <c r="B83" t="n">
         <v>0.208</v>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D83" t="n">
         <v>71</v>
       </c>
@@ -4388,7 +4714,9 @@
       <c r="H83" t="n">
         <v>21</v>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>23</v>
+      </c>
       <c r="J83" t="n">
         <v>59</v>
       </c>
@@ -4423,7 +4751,9 @@
       <c r="B84" t="n">
         <v>0.279</v>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>0.293</v>
+      </c>
       <c r="D84" t="n">
         <v>78</v>
       </c>
@@ -4435,7 +4765,9 @@
       <c r="H84" t="n">
         <v>21</v>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>21</v>
+      </c>
       <c r="J84" t="n">
         <v>82</v>
       </c>
@@ -4470,7 +4802,9 @@
       <c r="B85" t="n">
         <v>0.28</v>
       </c>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>0.258</v>
+      </c>
       <c r="D85" t="n">
         <v>55</v>
       </c>
@@ -4482,7 +4816,9 @@
       <c r="H85" t="n">
         <v>21</v>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>22</v>
+      </c>
       <c r="J85" t="n">
         <v>73</v>
       </c>
@@ -4517,7 +4853,9 @@
       <c r="B86" t="n">
         <v>0.178</v>
       </c>
-      <c r="C86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>0.202</v>
+      </c>
       <c r="D86" t="n">
         <v>53</v>
       </c>
@@ -4529,7 +4867,9 @@
       <c r="H86" t="n">
         <v>21</v>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>20</v>
+      </c>
       <c r="J86" t="n">
         <v>52</v>
       </c>
@@ -4564,7 +4904,9 @@
       <c r="B87" t="n">
         <v>0.206</v>
       </c>
-      <c r="C87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>0.217</v>
+      </c>
       <c r="D87" t="n">
         <v>46</v>
       </c>
@@ -4576,7 +4918,9 @@
       <c r="H87" t="n">
         <v>21</v>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>20</v>
+      </c>
       <c r="J87" t="n">
         <v>51</v>
       </c>
@@ -4611,7 +4955,9 @@
       <c r="B88" t="n">
         <v>0.251</v>
       </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>0.233</v>
+      </c>
       <c r="D88" t="n">
         <v>49</v>
       </c>
@@ -4623,7 +4969,9 @@
       <c r="H88" t="n">
         <v>21</v>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>20</v>
+      </c>
       <c r="J88" t="n">
         <v>62</v>
       </c>
@@ -4658,7 +5006,9 @@
       <c r="B89" t="n">
         <v>0.206</v>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="n">
+        <v>0.213</v>
+      </c>
       <c r="D89" t="n">
         <v>37</v>
       </c>
@@ -4670,7 +5020,9 @@
       <c r="H89" t="n">
         <v>21</v>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>20</v>
+      </c>
       <c r="J89" t="n">
         <v>50</v>
       </c>
@@ -4705,7 +5057,9 @@
       <c r="B90" t="n">
         <v>0.28</v>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>0.274</v>
+      </c>
       <c r="D90" t="n">
         <v>68</v>
       </c>
@@ -4717,7 +5071,9 @@
       <c r="H90" t="n">
         <v>20</v>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>21</v>
+      </c>
       <c r="J90" t="n">
         <v>67</v>
       </c>
@@ -4752,7 +5108,9 @@
       <c r="B91" t="n">
         <v>0.235</v>
       </c>
-      <c r="C91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>0.246</v>
+      </c>
       <c r="D91" t="n">
         <v>63</v>
       </c>
@@ -4764,7 +5122,9 @@
       <c r="H91" t="n">
         <v>20</v>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>21</v>
+      </c>
       <c r="J91" t="n">
         <v>56</v>
       </c>
@@ -4799,7 +5159,9 @@
       <c r="B92" t="n">
         <v>0.235</v>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>0.239</v>
+      </c>
       <c r="D92" t="n">
         <v>69</v>
       </c>
@@ -4811,7 +5173,9 @@
       <c r="H92" t="n">
         <v>20</v>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>19</v>
+      </c>
       <c r="J92" t="n">
         <v>58</v>
       </c>
@@ -4846,7 +5210,9 @@
       <c r="B93" t="n">
         <v>0.183</v>
       </c>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>0.196</v>
+      </c>
       <c r="D93" t="n">
         <v>45</v>
       </c>
@@ -4858,7 +5224,9 @@
       <c r="H93" t="n">
         <v>20</v>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>19</v>
+      </c>
       <c r="J93" t="n">
         <v>55</v>
       </c>
@@ -4893,7 +5261,9 @@
       <c r="B94" t="n">
         <v>0.23</v>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="n">
+        <v>0.206</v>
+      </c>
       <c r="D94" t="n">
         <v>43</v>
       </c>
@@ -4905,7 +5275,9 @@
       <c r="H94" t="n">
         <v>20</v>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>17</v>
+      </c>
       <c r="J94" t="n">
         <v>50</v>
       </c>
@@ -4940,7 +5312,9 @@
       <c r="B95" t="n">
         <v>0.266</v>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="n">
+        <v>0.268</v>
+      </c>
       <c r="D95" t="n">
         <v>46</v>
       </c>
@@ -4952,7 +5326,9 @@
       <c r="H95" t="n">
         <v>20</v>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>15</v>
+      </c>
       <c r="J95" t="n">
         <v>53</v>
       </c>
@@ -4987,7 +5363,9 @@
       <c r="B96" t="n">
         <v>0.221</v>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D96" t="n">
         <v>79</v>
       </c>
@@ -4999,7 +5377,9 @@
       <c r="H96" t="n">
         <v>20</v>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>19</v>
+      </c>
       <c r="J96" t="n">
         <v>73</v>
       </c>
@@ -5034,7 +5414,9 @@
       <c r="B97" t="n">
         <v>0.221</v>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D97" t="n">
         <v>47</v>
       </c>
@@ -5046,7 +5428,9 @@
       <c r="H97" t="n">
         <v>20</v>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>17</v>
+      </c>
       <c r="J97" t="n">
         <v>58</v>
       </c>
@@ -5081,7 +5465,9 @@
       <c r="B98" t="n">
         <v>0.298</v>
       </c>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="n">
+        <v>0.275</v>
+      </c>
       <c r="D98" t="n">
         <v>79</v>
       </c>
@@ -5093,7 +5479,9 @@
       <c r="H98" t="n">
         <v>19</v>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>17</v>
+      </c>
       <c r="J98" t="n">
         <v>64</v>
       </c>
@@ -5128,7 +5516,9 @@
       <c r="B99" t="n">
         <v>0.226</v>
       </c>
-      <c r="C99" t="inlineStr"/>
+      <c r="C99" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D99" t="n">
         <v>46</v>
       </c>
@@ -5140,7 +5530,9 @@
       <c r="H99" t="n">
         <v>19</v>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>17</v>
+      </c>
       <c r="J99" t="n">
         <v>54</v>
       </c>
@@ -5175,7 +5567,9 @@
       <c r="B100" t="n">
         <v>0.279</v>
       </c>
-      <c r="C100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>0.276</v>
+      </c>
       <c r="D100" t="n">
         <v>76</v>
       </c>
@@ -5187,7 +5581,9 @@
       <c r="H100" t="n">
         <v>19</v>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>18</v>
+      </c>
       <c r="J100" t="n">
         <v>68</v>
       </c>
@@ -5222,7 +5618,9 @@
       <c r="B101" t="n">
         <v>0.251</v>
       </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D101" t="n">
         <v>58</v>
       </c>
@@ -5234,7 +5632,9 @@
       <c r="H101" t="n">
         <v>19</v>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>17</v>
+      </c>
       <c r="J101" t="n">
         <v>62</v>
       </c>
@@ -5269,7 +5669,9 @@
       <c r="B102" t="n">
         <v>0.214</v>
       </c>
-      <c r="C102" t="inlineStr"/>
+      <c r="C102" t="n">
+        <v>0.205</v>
+      </c>
       <c r="D102" t="n">
         <v>43</v>
       </c>
@@ -5281,7 +5683,9 @@
       <c r="H102" t="n">
         <v>19</v>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>18</v>
+      </c>
       <c r="J102" t="n">
         <v>51</v>
       </c>
@@ -5316,7 +5720,9 @@
       <c r="B103" t="n">
         <v>0.228</v>
       </c>
-      <c r="C103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>0.244</v>
+      </c>
       <c r="D103" t="n">
         <v>70</v>
       </c>
@@ -5328,7 +5734,9 @@
       <c r="H103" t="n">
         <v>19</v>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>20</v>
+      </c>
       <c r="J103" t="n">
         <v>74</v>
       </c>
@@ -5363,7 +5771,9 @@
       <c r="B104" t="n">
         <v>0.257</v>
       </c>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D104" t="n">
         <v>71</v>
       </c>
@@ -5375,7 +5785,9 @@
       <c r="H104" t="n">
         <v>19</v>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>18</v>
+      </c>
       <c r="J104" t="n">
         <v>72</v>
       </c>
@@ -5410,7 +5822,9 @@
       <c r="B105" t="n">
         <v>0.218</v>
       </c>
-      <c r="C105" t="inlineStr"/>
+      <c r="C105" t="n">
+        <v>0.218</v>
+      </c>
       <c r="D105" t="n">
         <v>41</v>
       </c>
@@ -5422,7 +5836,9 @@
       <c r="H105" t="n">
         <v>19</v>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>18</v>
+      </c>
       <c r="J105" t="n">
         <v>52</v>
       </c>
@@ -5457,7 +5873,9 @@
       <c r="B106" t="n">
         <v>0.289</v>
       </c>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D106" t="n">
         <v>48</v>
       </c>
@@ -5469,7 +5887,9 @@
       <c r="H106" t="n">
         <v>19</v>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>22</v>
+      </c>
       <c r="J106" t="n">
         <v>71</v>
       </c>
@@ -5504,7 +5924,9 @@
       <c r="B107" t="n">
         <v>0.229</v>
       </c>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D107" t="n">
         <v>71</v>
       </c>
@@ -5516,7 +5938,9 @@
       <c r="H107" t="n">
         <v>19</v>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>22</v>
+      </c>
       <c r="J107" t="n">
         <v>64</v>
       </c>
@@ -5551,7 +5975,9 @@
       <c r="B108" t="n">
         <v>0.258</v>
       </c>
-      <c r="C108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D108" t="n">
         <v>48</v>
       </c>
@@ -5563,7 +5989,9 @@
       <c r="H108" t="n">
         <v>18</v>
       </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>16</v>
+      </c>
       <c r="J108" t="n">
         <v>60</v>
       </c>
@@ -5598,7 +6026,9 @@
       <c r="B109" t="n">
         <v>0.329</v>
       </c>
-      <c r="C109" t="inlineStr"/>
+      <c r="C109" t="n">
+        <v>0.305</v>
+      </c>
       <c r="D109" t="n">
         <v>95</v>
       </c>
@@ -5610,7 +6040,9 @@
       <c r="H109" t="n">
         <v>18</v>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>18</v>
+      </c>
       <c r="J109" t="n">
         <v>65</v>
       </c>
@@ -5645,7 +6077,9 @@
       <c r="B110" t="n">
         <v>0.236</v>
       </c>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="n">
+        <v>0.245</v>
+      </c>
       <c r="D110" t="n">
         <v>83</v>
       </c>
@@ -5657,7 +6091,9 @@
       <c r="H110" t="n">
         <v>18</v>
       </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>19</v>
+      </c>
       <c r="J110" t="n">
         <v>78</v>
       </c>
@@ -5692,7 +6128,9 @@
       <c r="B111" t="n">
         <v>0.199</v>
       </c>
-      <c r="C111" t="inlineStr"/>
+      <c r="C111" t="n">
+        <v>0.206</v>
+      </c>
       <c r="D111" t="n">
         <v>53</v>
       </c>
@@ -5704,7 +6142,9 @@
       <c r="H111" t="n">
         <v>18</v>
       </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>18</v>
+      </c>
       <c r="J111" t="n">
         <v>57</v>
       </c>
@@ -5739,7 +6179,9 @@
       <c r="B112" t="n">
         <v>0.248</v>
       </c>
-      <c r="C112" t="inlineStr"/>
+      <c r="C112" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D112" t="n">
         <v>79</v>
       </c>
@@ -5751,7 +6193,9 @@
       <c r="H112" t="n">
         <v>18</v>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>18</v>
+      </c>
       <c r="J112" t="n">
         <v>61</v>
       </c>
@@ -5786,7 +6230,9 @@
       <c r="B113" t="n">
         <v>0.198</v>
       </c>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D113" t="n">
         <v>65</v>
       </c>
@@ -5798,7 +6244,9 @@
       <c r="H113" t="n">
         <v>18</v>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>20</v>
+      </c>
       <c r="J113" t="n">
         <v>55</v>
       </c>
@@ -5833,7 +6281,9 @@
       <c r="B114" t="n">
         <v>0.229</v>
       </c>
-      <c r="C114" t="inlineStr"/>
+      <c r="C114" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D114" t="n">
         <v>55</v>
       </c>
@@ -5845,7 +6295,9 @@
       <c r="H114" t="n">
         <v>18</v>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>18</v>
+      </c>
       <c r="J114" t="n">
         <v>59</v>
       </c>
@@ -5880,7 +6332,9 @@
       <c r="B115" t="n">
         <v>0.213</v>
       </c>
-      <c r="C115" t="inlineStr"/>
+      <c r="C115" t="n">
+        <v>0.228</v>
+      </c>
       <c r="D115" t="n">
         <v>45</v>
       </c>
@@ -5892,7 +6346,9 @@
       <c r="H115" t="n">
         <v>18</v>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>22</v>
+      </c>
       <c r="J115" t="n">
         <v>50</v>
       </c>
@@ -5927,7 +6383,9 @@
       <c r="B116" t="n">
         <v>0.274</v>
       </c>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="n">
+        <v>0.273</v>
+      </c>
       <c r="D116" t="n">
         <v>62</v>
       </c>
@@ -5939,7 +6397,9 @@
       <c r="H116" t="n">
         <v>18</v>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>20</v>
+      </c>
       <c r="J116" t="n">
         <v>64</v>
       </c>
@@ -5974,7 +6434,9 @@
       <c r="B117" t="n">
         <v>0.278</v>
       </c>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="n">
+        <v>0.275</v>
+      </c>
       <c r="D117" t="n">
         <v>77</v>
       </c>
@@ -5986,7 +6448,9 @@
       <c r="H117" t="n">
         <v>18</v>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>18</v>
+      </c>
       <c r="J117" t="n">
         <v>79</v>
       </c>
@@ -6021,7 +6485,9 @@
       <c r="B118" t="n">
         <v>0.283</v>
       </c>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="n">
+        <v>0.29</v>
+      </c>
       <c r="D118" t="n">
         <v>60</v>
       </c>
@@ -6033,7 +6499,9 @@
       <c r="H118" t="n">
         <v>18</v>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>16</v>
+      </c>
       <c r="J118" t="n">
         <v>62</v>
       </c>
@@ -6068,7 +6536,9 @@
       <c r="B119" t="n">
         <v>0.183</v>
       </c>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>0.218</v>
+      </c>
       <c r="D119" t="n">
         <v>56</v>
       </c>
@@ -6080,7 +6550,9 @@
       <c r="H119" t="n">
         <v>18</v>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>20</v>
+      </c>
       <c r="J119" t="n">
         <v>55</v>
       </c>
@@ -6115,7 +6587,9 @@
       <c r="B120" t="n">
         <v>0.248</v>
       </c>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D120" t="n">
         <v>62</v>
       </c>
@@ -6127,7 +6601,9 @@
       <c r="H120" t="n">
         <v>18</v>
       </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>18</v>
+      </c>
       <c r="J120" t="n">
         <v>63</v>
       </c>
@@ -6162,7 +6638,9 @@
       <c r="B121" t="n">
         <v>0.248</v>
       </c>
-      <c r="C121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D121" t="n">
         <v>84</v>
       </c>
@@ -6174,7 +6652,9 @@
       <c r="H121" t="n">
         <v>17</v>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>15</v>
+      </c>
       <c r="J121" t="n">
         <v>73</v>
       </c>
@@ -6209,7 +6689,9 @@
       <c r="B122" t="n">
         <v>0.247</v>
       </c>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D122" t="n">
         <v>50</v>
       </c>
@@ -6221,7 +6703,9 @@
       <c r="H122" t="n">
         <v>17</v>
       </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>15</v>
+      </c>
       <c r="J122" t="n">
         <v>52</v>
       </c>
@@ -6256,7 +6740,9 @@
       <c r="B123" t="n">
         <v>0.275</v>
       </c>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D123" t="n">
         <v>96</v>
       </c>
@@ -6268,7 +6754,9 @@
       <c r="H123" t="n">
         <v>17</v>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>15</v>
+      </c>
       <c r="J123" t="n">
         <v>86</v>
       </c>
@@ -6303,7 +6791,9 @@
       <c r="B124" t="n">
         <v>0.245</v>
       </c>
-      <c r="C124" t="inlineStr"/>
+      <c r="C124" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D124" t="n">
         <v>63</v>
       </c>
@@ -6315,7 +6805,9 @@
       <c r="H124" t="n">
         <v>17</v>
       </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>17</v>
+      </c>
       <c r="J124" t="n">
         <v>59</v>
       </c>
@@ -6350,7 +6842,9 @@
       <c r="B125" t="n">
         <v>0.279</v>
       </c>
-      <c r="C125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D125" t="n">
         <v>63</v>
       </c>
@@ -6362,7 +6856,9 @@
       <c r="H125" t="n">
         <v>17</v>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>18</v>
+      </c>
       <c r="J125" t="n">
         <v>76</v>
       </c>
@@ -6397,7 +6893,9 @@
       <c r="B126" t="n">
         <v>0.237</v>
       </c>
-      <c r="C126" t="inlineStr"/>
+      <c r="C126" t="n">
+        <v>0.22</v>
+      </c>
       <c r="D126" t="n">
         <v>48</v>
       </c>
@@ -6409,7 +6907,9 @@
       <c r="H126" t="n">
         <v>16</v>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="n">
+        <v>14</v>
+      </c>
       <c r="J126" t="n">
         <v>51</v>
       </c>
@@ -6444,7 +6944,9 @@
       <c r="B127" t="n">
         <v>0.252</v>
       </c>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="n">
+        <v>0.174</v>
+      </c>
       <c r="D127" t="n">
         <v>49</v>
       </c>
@@ -6456,7 +6958,9 @@
       <c r="H127" t="n">
         <v>16</v>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="n">
+        <v>15</v>
+      </c>
       <c r="J127" t="n">
         <v>58</v>
       </c>
@@ -6491,7 +6995,9 @@
       <c r="B128" t="n">
         <v>0.254</v>
       </c>
-      <c r="C128" t="inlineStr"/>
+      <c r="C128" t="n">
+        <v>0.253</v>
+      </c>
       <c r="D128" t="n">
         <v>51</v>
       </c>
@@ -6503,7 +7009,9 @@
       <c r="H128" t="n">
         <v>16</v>
       </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="n">
+        <v>16</v>
+      </c>
       <c r="J128" t="n">
         <v>49</v>
       </c>
@@ -6538,7 +7046,9 @@
       <c r="B129" t="n">
         <v>0.243</v>
       </c>
-      <c r="C129" t="inlineStr"/>
+      <c r="C129" t="n">
+        <v>0.254</v>
+      </c>
       <c r="D129" t="n">
         <v>60</v>
       </c>
@@ -6550,7 +7060,9 @@
       <c r="H129" t="n">
         <v>16</v>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>18</v>
+      </c>
       <c r="J129" t="n">
         <v>72</v>
       </c>
@@ -6585,7 +7097,9 @@
       <c r="B130" t="n">
         <v>0.262</v>
       </c>
-      <c r="C130" t="inlineStr"/>
+      <c r="C130" t="n">
+        <v>0.245</v>
+      </c>
       <c r="D130" t="n">
         <v>74</v>
       </c>
@@ -6597,7 +7111,9 @@
       <c r="H130" t="n">
         <v>16</v>
       </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>13</v>
+      </c>
       <c r="J130" t="n">
         <v>70</v>
       </c>
@@ -6632,7 +7148,9 @@
       <c r="B131" t="n">
         <v>0.265</v>
       </c>
-      <c r="C131" t="inlineStr"/>
+      <c r="C131" t="n">
+        <v>0.259</v>
+      </c>
       <c r="D131" t="n">
         <v>66</v>
       </c>
@@ -6644,7 +7162,9 @@
       <c r="H131" t="n">
         <v>16</v>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="n">
+        <v>16</v>
+      </c>
       <c r="J131" t="n">
         <v>54</v>
       </c>
@@ -6679,7 +7199,9 @@
       <c r="B132" t="n">
         <v>0.307</v>
       </c>
-      <c r="C132" t="inlineStr"/>
+      <c r="C132" t="n">
+        <v>0.304</v>
+      </c>
       <c r="D132" t="n">
         <v>69</v>
       </c>
@@ -6691,7 +7213,9 @@
       <c r="H132" t="n">
         <v>16</v>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="n">
+        <v>19</v>
+      </c>
       <c r="J132" t="n">
         <v>76</v>
       </c>
@@ -6726,7 +7250,9 @@
       <c r="B133" t="n">
         <v>0.255</v>
       </c>
-      <c r="C133" t="inlineStr"/>
+      <c r="C133" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D133" t="n">
         <v>70</v>
       </c>
@@ -6738,7 +7264,9 @@
       <c r="H133" t="n">
         <v>16</v>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="n">
+        <v>12</v>
+      </c>
       <c r="J133" t="n">
         <v>63</v>
       </c>
@@ -6773,7 +7301,9 @@
       <c r="B134" t="n">
         <v>0.232</v>
       </c>
-      <c r="C134" t="inlineStr"/>
+      <c r="C134" t="n">
+        <v>0.237</v>
+      </c>
       <c r="D134" t="n">
         <v>63</v>
       </c>
@@ -6785,7 +7315,9 @@
       <c r="H134" t="n">
         <v>16</v>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="n">
+        <v>15</v>
+      </c>
       <c r="J134" t="n">
         <v>55</v>
       </c>
@@ -6820,7 +7352,9 @@
       <c r="B135" t="n">
         <v>0.281</v>
       </c>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="n">
+        <v>0.274</v>
+      </c>
       <c r="D135" t="n">
         <v>51</v>
       </c>
@@ -6832,7 +7366,9 @@
       <c r="H135" t="n">
         <v>16</v>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="n">
+        <v>16</v>
+      </c>
       <c r="J135" t="n">
         <v>67</v>
       </c>
@@ -6867,7 +7403,9 @@
       <c r="B136" t="n">
         <v>0.261</v>
       </c>
-      <c r="C136" t="inlineStr"/>
+      <c r="C136" t="n">
+        <v>0.269</v>
+      </c>
       <c r="D136" t="n">
         <v>74</v>
       </c>
@@ -6879,7 +7417,9 @@
       <c r="H136" t="n">
         <v>16</v>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="n">
+        <v>18</v>
+      </c>
       <c r="J136" t="n">
         <v>70</v>
       </c>
@@ -6914,7 +7454,9 @@
       <c r="B137" t="n">
         <v>0.243</v>
       </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="C137" t="n">
+        <v>0.243</v>
+      </c>
       <c r="D137" t="n">
         <v>54</v>
       </c>
@@ -6926,7 +7468,9 @@
       <c r="H137" t="n">
         <v>16</v>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>18</v>
+      </c>
       <c r="J137" t="n">
         <v>58</v>
       </c>
@@ -6961,7 +7505,9 @@
       <c r="B138" t="n">
         <v>0.241</v>
       </c>
-      <c r="C138" t="inlineStr"/>
+      <c r="C138" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D138" t="n">
         <v>59</v>
       </c>
@@ -6973,7 +7519,9 @@
       <c r="H138" t="n">
         <v>16</v>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>17</v>
+      </c>
       <c r="J138" t="n">
         <v>52</v>
       </c>
@@ -7008,7 +7556,9 @@
       <c r="B139" t="n">
         <v>0.269</v>
       </c>
-      <c r="C139" t="inlineStr"/>
+      <c r="C139" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D139" t="n">
         <v>95</v>
       </c>
@@ -7020,7 +7570,9 @@
       <c r="H139" t="n">
         <v>16</v>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="n">
+        <v>21</v>
+      </c>
       <c r="J139" t="n">
         <v>35</v>
       </c>
@@ -7055,7 +7607,9 @@
       <c r="B140" t="n">
         <v>0.231</v>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D140" t="n">
         <v>48</v>
       </c>
@@ -7067,7 +7621,9 @@
       <c r="H140" t="n">
         <v>15</v>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="n">
+        <v>18</v>
+      </c>
       <c r="J140" t="n">
         <v>56</v>
       </c>
@@ -7102,7 +7658,9 @@
       <c r="B141" t="n">
         <v>0.225</v>
       </c>
-      <c r="C141" t="inlineStr"/>
+      <c r="C141" t="n">
+        <v>0.22</v>
+      </c>
       <c r="D141" t="n">
         <v>55</v>
       </c>
@@ -7114,7 +7672,9 @@
       <c r="H141" t="n">
         <v>15</v>
       </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="n">
+        <v>15</v>
+      </c>
       <c r="J141" t="n">
         <v>42</v>
       </c>
@@ -7149,7 +7709,9 @@
       <c r="B142" t="n">
         <v>0.223</v>
       </c>
-      <c r="C142" t="inlineStr"/>
+      <c r="C142" t="n">
+        <v>0.236</v>
+      </c>
       <c r="D142" t="n">
         <v>37</v>
       </c>
@@ -7161,7 +7723,9 @@
       <c r="H142" t="n">
         <v>15</v>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="n">
+        <v>16</v>
+      </c>
       <c r="J142" t="n">
         <v>53</v>
       </c>
@@ -7196,7 +7760,9 @@
       <c r="B143" t="n">
         <v>0.272</v>
       </c>
-      <c r="C143" t="inlineStr"/>
+      <c r="C143" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D143" t="n">
         <v>54</v>
       </c>
@@ -7208,7 +7774,9 @@
       <c r="H143" t="n">
         <v>15</v>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="n">
+        <v>14</v>
+      </c>
       <c r="J143" t="n">
         <v>55</v>
       </c>
@@ -7243,7 +7811,9 @@
       <c r="B144" t="n">
         <v>0.23</v>
       </c>
-      <c r="C144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>0.236</v>
+      </c>
       <c r="D144" t="n">
         <v>64</v>
       </c>
@@ -7255,7 +7825,9 @@
       <c r="H144" t="n">
         <v>15</v>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>15</v>
+      </c>
       <c r="J144" t="n">
         <v>58</v>
       </c>
@@ -7290,7 +7862,9 @@
       <c r="B145" t="n">
         <v>0.233</v>
       </c>
-      <c r="C145" t="inlineStr"/>
+      <c r="C145" t="n">
+        <v>0.202</v>
+      </c>
       <c r="D145" t="n">
         <v>54</v>
       </c>
@@ -7302,7 +7876,9 @@
       <c r="H145" t="n">
         <v>15</v>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="n">
+        <v>13</v>
+      </c>
       <c r="J145" t="n">
         <v>45</v>
       </c>
@@ -7337,7 +7913,9 @@
       <c r="B146" t="n">
         <v>0.236</v>
       </c>
-      <c r="C146" t="inlineStr"/>
+      <c r="C146" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D146" t="n">
         <v>49</v>
       </c>
@@ -7349,7 +7927,9 @@
       <c r="H146" t="n">
         <v>15</v>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>21</v>
+      </c>
       <c r="J146" t="n">
         <v>59</v>
       </c>
@@ -7384,7 +7964,9 @@
       <c r="B147" t="n">
         <v>0.255</v>
       </c>
-      <c r="C147" t="inlineStr"/>
+      <c r="C147" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D147" t="n">
         <v>45</v>
       </c>
@@ -7396,7 +7978,9 @@
       <c r="H147" t="n">
         <v>15</v>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="n">
+        <v>15</v>
+      </c>
       <c r="J147" t="n">
         <v>62</v>
       </c>
@@ -7431,7 +8015,9 @@
       <c r="B148" t="n">
         <v>0.241</v>
       </c>
-      <c r="C148" t="inlineStr"/>
+      <c r="C148" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D148" t="n">
         <v>52</v>
       </c>
@@ -7443,7 +8029,9 @@
       <c r="H148" t="n">
         <v>15</v>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="n">
+        <v>15</v>
+      </c>
       <c r="J148" t="n">
         <v>56</v>
       </c>
@@ -7478,7 +8066,9 @@
       <c r="B149" t="n">
         <v>0.188</v>
       </c>
-      <c r="C149" t="inlineStr"/>
+      <c r="C149" t="n">
+        <v>0.201</v>
+      </c>
       <c r="D149" t="n">
         <v>44</v>
       </c>
@@ -7490,7 +8080,9 @@
       <c r="H149" t="n">
         <v>15</v>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>15</v>
+      </c>
       <c r="J149" t="n">
         <v>50</v>
       </c>
@@ -7525,7 +8117,9 @@
       <c r="B150" t="n">
         <v>0.292</v>
       </c>
-      <c r="C150" t="inlineStr"/>
+      <c r="C150" t="n">
+        <v>0.297</v>
+      </c>
       <c r="D150" t="n">
         <v>88</v>
       </c>
@@ -7537,7 +8131,9 @@
       <c r="H150" t="n">
         <v>15</v>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="n">
+        <v>13</v>
+      </c>
       <c r="J150" t="n">
         <v>66</v>
       </c>
@@ -7572,7 +8168,9 @@
       <c r="B151" t="n">
         <v>0.283</v>
       </c>
-      <c r="C151" t="inlineStr"/>
+      <c r="C151" t="n">
+        <v>0.282</v>
+      </c>
       <c r="D151" t="n">
         <v>61</v>
       </c>
@@ -7584,7 +8182,9 @@
       <c r="H151" t="n">
         <v>15</v>
       </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="n">
+        <v>14</v>
+      </c>
       <c r="J151" t="n">
         <v>59</v>
       </c>
@@ -7619,7 +8219,9 @@
       <c r="B152" t="n">
         <v>0.233</v>
       </c>
-      <c r="C152" t="inlineStr"/>
+      <c r="C152" t="n">
+        <v>0.235</v>
+      </c>
       <c r="D152" t="n">
         <v>55</v>
       </c>
@@ -7631,7 +8233,9 @@
       <c r="H152" t="n">
         <v>15</v>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>14</v>
+      </c>
       <c r="J152" t="n">
         <v>47</v>
       </c>
@@ -7666,7 +8270,9 @@
       <c r="B153" t="n">
         <v>0.226</v>
       </c>
-      <c r="C153" t="inlineStr"/>
+      <c r="C153" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D153" t="n">
         <v>50</v>
       </c>
@@ -7678,7 +8284,9 @@
       <c r="H153" t="n">
         <v>15</v>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>17</v>
+      </c>
       <c r="J153" t="n">
         <v>54</v>
       </c>
@@ -7713,7 +8321,9 @@
       <c r="B154" t="n">
         <v>0.268</v>
       </c>
-      <c r="C154" t="inlineStr"/>
+      <c r="C154" t="n">
+        <v>0.271</v>
+      </c>
       <c r="D154" t="n">
         <v>48</v>
       </c>
@@ -7725,7 +8335,9 @@
       <c r="H154" t="n">
         <v>15</v>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="n">
+        <v>12</v>
+      </c>
       <c r="J154" t="n">
         <v>49</v>
       </c>
@@ -7760,7 +8372,9 @@
       <c r="B155" t="n">
         <v>0.181</v>
       </c>
-      <c r="C155" t="inlineStr"/>
+      <c r="C155" t="n">
+        <v>0.194</v>
+      </c>
       <c r="D155" t="n">
         <v>42</v>
       </c>
@@ -7772,7 +8386,9 @@
       <c r="H155" t="n">
         <v>14</v>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="n">
+        <v>17</v>
+      </c>
       <c r="J155" t="n">
         <v>50</v>
       </c>
@@ -7807,7 +8423,9 @@
       <c r="B156" t="n">
         <v>0.244</v>
       </c>
-      <c r="C156" t="inlineStr"/>
+      <c r="C156" t="n">
+        <v>0.254</v>
+      </c>
       <c r="D156" t="n">
         <v>38</v>
       </c>
@@ -7819,7 +8437,9 @@
       <c r="H156" t="n">
         <v>14</v>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>12</v>
+      </c>
       <c r="J156" t="n">
         <v>46</v>
       </c>
@@ -7854,7 +8474,9 @@
       <c r="B157" t="n">
         <v>0.231</v>
       </c>
-      <c r="C157" t="inlineStr"/>
+      <c r="C157" t="n">
+        <v>0.209</v>
+      </c>
       <c r="D157" t="n">
         <v>48</v>
       </c>
@@ -7866,7 +8488,9 @@
       <c r="H157" t="n">
         <v>14</v>
       </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="I157" t="n">
+        <v>14</v>
+      </c>
       <c r="J157" t="n">
         <v>47</v>
       </c>
@@ -7901,7 +8525,9 @@
       <c r="B158" t="n">
         <v>0.231</v>
       </c>
-      <c r="C158" t="inlineStr"/>
+      <c r="C158" t="n">
+        <v>0.244</v>
+      </c>
       <c r="D158" t="n">
         <v>49</v>
       </c>
@@ -7913,7 +8539,9 @@
       <c r="H158" t="n">
         <v>14</v>
       </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="I158" t="n">
+        <v>13</v>
+      </c>
       <c r="J158" t="n">
         <v>51</v>
       </c>
@@ -7948,7 +8576,9 @@
       <c r="B159" t="n">
         <v>0.276</v>
       </c>
-      <c r="C159" t="inlineStr"/>
+      <c r="C159" t="n">
+        <v>0.285</v>
+      </c>
       <c r="D159" t="n">
         <v>61</v>
       </c>
@@ -7960,7 +8590,9 @@
       <c r="H159" t="n">
         <v>14</v>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="n">
+        <v>13</v>
+      </c>
       <c r="J159" t="n">
         <v>56</v>
       </c>
@@ -7995,7 +8627,9 @@
       <c r="B160" t="n">
         <v>0.278</v>
       </c>
-      <c r="C160" t="inlineStr"/>
+      <c r="C160" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D160" t="n">
         <v>86</v>
       </c>
@@ -8007,7 +8641,9 @@
       <c r="H160" t="n">
         <v>14</v>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="n">
+        <v>12</v>
+      </c>
       <c r="J160" t="n">
         <v>62</v>
       </c>
@@ -8042,7 +8678,9 @@
       <c r="B161" t="n">
         <v>0.234</v>
       </c>
-      <c r="C161" t="inlineStr"/>
+      <c r="C161" t="n">
+        <v>0.24</v>
+      </c>
       <c r="D161" t="n">
         <v>44</v>
       </c>
@@ -8054,7 +8692,9 @@
       <c r="H161" t="n">
         <v>14</v>
       </c>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>14</v>
+      </c>
       <c r="J161" t="n">
         <v>41</v>
       </c>
@@ -8089,7 +8729,9 @@
       <c r="B162" t="n">
         <v>0.233</v>
       </c>
-      <c r="C162" t="inlineStr"/>
+      <c r="C162" t="n">
+        <v>0.212</v>
+      </c>
       <c r="D162" t="n">
         <v>50</v>
       </c>
@@ -8101,7 +8743,9 @@
       <c r="H162" t="n">
         <v>14</v>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>12</v>
+      </c>
       <c r="J162" t="n">
         <v>48</v>
       </c>
@@ -8136,7 +8780,9 @@
       <c r="B163" t="n">
         <v>0.272</v>
       </c>
-      <c r="C163" t="inlineStr"/>
+      <c r="C163" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D163" t="n">
         <v>70</v>
       </c>
@@ -8148,7 +8794,9 @@
       <c r="H163" t="n">
         <v>14</v>
       </c>
-      <c r="I163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>13</v>
+      </c>
       <c r="J163" t="n">
         <v>52</v>
       </c>
@@ -8183,7 +8831,9 @@
       <c r="B164" t="n">
         <v>0.273</v>
       </c>
-      <c r="C164" t="inlineStr"/>
+      <c r="C164" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D164" t="n">
         <v>57</v>
       </c>
@@ -8195,7 +8845,9 @@
       <c r="H164" t="n">
         <v>14</v>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="n">
+        <v>13</v>
+      </c>
       <c r="J164" t="n">
         <v>52</v>
       </c>
@@ -8230,7 +8882,9 @@
       <c r="B165" t="n">
         <v>0.208</v>
       </c>
-      <c r="C165" t="inlineStr"/>
+      <c r="C165" t="n">
+        <v>0.209</v>
+      </c>
       <c r="D165" t="n">
         <v>35</v>
       </c>
@@ -8242,7 +8896,9 @@
       <c r="H165" t="n">
         <v>14</v>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>13</v>
+      </c>
       <c r="J165" t="n">
         <v>42</v>
       </c>
@@ -8277,7 +8933,9 @@
       <c r="B166" t="n">
         <v>0.231</v>
       </c>
-      <c r="C166" t="inlineStr"/>
+      <c r="C166" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D166" t="n">
         <v>46</v>
       </c>
@@ -8289,7 +8947,9 @@
       <c r="H166" t="n">
         <v>14</v>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>11</v>
+      </c>
       <c r="J166" t="n">
         <v>36</v>
       </c>
@@ -8324,7 +8984,9 @@
       <c r="B167" t="n">
         <v>0.249</v>
       </c>
-      <c r="C167" t="inlineStr"/>
+      <c r="C167" t="n">
+        <v>0.235</v>
+      </c>
       <c r="D167" t="n">
         <v>60</v>
       </c>
@@ -8336,7 +8998,9 @@
       <c r="H167" t="n">
         <v>14</v>
       </c>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>14</v>
+      </c>
       <c r="J167" t="n">
         <v>54</v>
       </c>
@@ -8371,7 +9035,9 @@
       <c r="B168" t="n">
         <v>0.262</v>
       </c>
-      <c r="C168" t="inlineStr"/>
+      <c r="C168" t="n">
+        <v>0.249</v>
+      </c>
       <c r="D168" t="n">
         <v>66</v>
       </c>
@@ -8383,7 +9049,9 @@
       <c r="H168" t="n">
         <v>14</v>
       </c>
-      <c r="I168" t="inlineStr"/>
+      <c r="I168" t="n">
+        <v>11</v>
+      </c>
       <c r="J168" t="n">
         <v>55</v>
       </c>
@@ -8418,7 +9086,9 @@
       <c r="B169" t="n">
         <v>0.275</v>
       </c>
-      <c r="C169" t="inlineStr"/>
+      <c r="C169" t="n">
+        <v>0.283</v>
+      </c>
       <c r="D169" t="n">
         <v>66</v>
       </c>
@@ -8430,7 +9100,9 @@
       <c r="H169" t="n">
         <v>14</v>
       </c>
-      <c r="I169" t="inlineStr"/>
+      <c r="I169" t="n">
+        <v>13</v>
+      </c>
       <c r="J169" t="n">
         <v>56</v>
       </c>
@@ -8465,7 +9137,9 @@
       <c r="B170" t="n">
         <v>0.243</v>
       </c>
-      <c r="C170" t="inlineStr"/>
+      <c r="C170" t="n">
+        <v>0.262</v>
+      </c>
       <c r="D170" t="n">
         <v>52</v>
       </c>
@@ -8477,7 +9151,9 @@
       <c r="H170" t="n">
         <v>14</v>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="n">
+        <v>12</v>
+      </c>
       <c r="J170" t="n">
         <v>50</v>
       </c>
@@ -8512,7 +9188,9 @@
       <c r="B171" t="n">
         <v>0.195</v>
       </c>
-      <c r="C171" t="inlineStr"/>
+      <c r="C171" t="n">
+        <v>0.209</v>
+      </c>
       <c r="D171" t="n">
         <v>44</v>
       </c>
@@ -8524,7 +9202,9 @@
       <c r="H171" t="n">
         <v>14</v>
       </c>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>15</v>
+      </c>
       <c r="J171" t="n">
         <v>46</v>
       </c>
@@ -8559,7 +9239,9 @@
       <c r="B172" t="n">
         <v>0.261</v>
       </c>
-      <c r="C172" t="inlineStr"/>
+      <c r="C172" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D172" t="n">
         <v>38</v>
       </c>
@@ -8571,7 +9253,9 @@
       <c r="H172" t="n">
         <v>14</v>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>12</v>
+      </c>
       <c r="J172" t="n">
         <v>45</v>
       </c>
@@ -8606,7 +9290,9 @@
       <c r="B173" t="n">
         <v>0.234</v>
       </c>
-      <c r="C173" t="inlineStr"/>
+      <c r="C173" t="n">
+        <v>0.206</v>
+      </c>
       <c r="D173" t="n">
         <v>75</v>
       </c>
@@ -8618,7 +9304,9 @@
       <c r="H173" t="n">
         <v>14</v>
       </c>
-      <c r="I173" t="inlineStr"/>
+      <c r="I173" t="n">
+        <v>14</v>
+      </c>
       <c r="J173" t="n">
         <v>67</v>
       </c>
@@ -8653,7 +9341,9 @@
       <c r="B174" t="n">
         <v>0.24</v>
       </c>
-      <c r="C174" t="inlineStr"/>
+      <c r="C174" t="n">
+        <v>0.235</v>
+      </c>
       <c r="D174" t="n">
         <v>39</v>
       </c>
@@ -8665,7 +9355,9 @@
       <c r="H174" t="n">
         <v>14</v>
       </c>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="n">
+        <v>13</v>
+      </c>
       <c r="J174" t="n">
         <v>56</v>
       </c>
@@ -8700,7 +9392,9 @@
       <c r="B175" t="n">
         <v>0.292</v>
       </c>
-      <c r="C175" t="inlineStr"/>
+      <c r="C175" t="n">
+        <v>0.268</v>
+      </c>
       <c r="D175" t="n">
         <v>61</v>
       </c>
@@ -8712,7 +9406,9 @@
       <c r="H175" t="n">
         <v>14</v>
       </c>
-      <c r="I175" t="inlineStr"/>
+      <c r="I175" t="n">
+        <v>17</v>
+      </c>
       <c r="J175" t="n">
         <v>60</v>
       </c>
@@ -8747,7 +9443,9 @@
       <c r="B176" t="n">
         <v>0.25</v>
       </c>
-      <c r="C176" t="inlineStr"/>
+      <c r="C176" t="n">
+        <v>0.258</v>
+      </c>
       <c r="D176" t="n">
         <v>43</v>
       </c>
@@ -8759,7 +9457,9 @@
       <c r="H176" t="n">
         <v>13</v>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>12</v>
+      </c>
       <c r="J176" t="n">
         <v>51</v>
       </c>
@@ -8794,7 +9494,9 @@
       <c r="B177" t="n">
         <v>0.274</v>
       </c>
-      <c r="C177" t="inlineStr"/>
+      <c r="C177" t="n">
+        <v>0.28</v>
+      </c>
       <c r="D177" t="n">
         <v>63</v>
       </c>
@@ -8806,7 +9508,9 @@
       <c r="H177" t="n">
         <v>13</v>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="n">
+        <v>14</v>
+      </c>
       <c r="J177" t="n">
         <v>56</v>
       </c>
@@ -8841,7 +9545,9 @@
       <c r="B178" t="n">
         <v>0.238</v>
       </c>
-      <c r="C178" t="inlineStr"/>
+      <c r="C178" t="n">
+        <v>0.251</v>
+      </c>
       <c r="D178" t="n">
         <v>51</v>
       </c>
@@ -8853,7 +9559,9 @@
       <c r="H178" t="n">
         <v>13</v>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="n">
+        <v>14</v>
+      </c>
       <c r="J178" t="n">
         <v>54</v>
       </c>
@@ -8888,7 +9596,9 @@
       <c r="B179" t="n">
         <v>0.225</v>
       </c>
-      <c r="C179" t="inlineStr"/>
+      <c r="C179" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D179" t="n">
         <v>45</v>
       </c>
@@ -8900,7 +9610,9 @@
       <c r="H179" t="n">
         <v>13</v>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>15</v>
+      </c>
       <c r="J179" t="n">
         <v>38</v>
       </c>
@@ -8935,7 +9647,9 @@
       <c r="B180" t="n">
         <v>0.232</v>
       </c>
-      <c r="C180" t="inlineStr"/>
+      <c r="C180" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D180" t="n">
         <v>43</v>
       </c>
@@ -8947,7 +9661,9 @@
       <c r="H180" t="n">
         <v>13</v>
       </c>
-      <c r="I180" t="inlineStr"/>
+      <c r="I180" t="n">
+        <v>13</v>
+      </c>
       <c r="J180" t="n">
         <v>44</v>
       </c>
@@ -8982,7 +9698,9 @@
       <c r="B181" t="n">
         <v>0.197</v>
       </c>
-      <c r="C181" t="inlineStr"/>
+      <c r="C181" t="n">
+        <v>0.2</v>
+      </c>
       <c r="D181" t="n">
         <v>34</v>
       </c>
@@ -8994,7 +9712,9 @@
       <c r="H181" t="n">
         <v>13</v>
       </c>
-      <c r="I181" t="inlineStr"/>
+      <c r="I181" t="n">
+        <v>14</v>
+      </c>
       <c r="J181" t="n">
         <v>48</v>
       </c>
@@ -9029,7 +9749,9 @@
       <c r="B182" t="n">
         <v>0.226</v>
       </c>
-      <c r="C182" t="inlineStr"/>
+      <c r="C182" t="n">
+        <v>0.236</v>
+      </c>
       <c r="D182" t="n">
         <v>54</v>
       </c>
@@ -9041,7 +9763,9 @@
       <c r="H182" t="n">
         <v>13</v>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="n">
+        <v>13</v>
+      </c>
       <c r="J182" t="n">
         <v>51</v>
       </c>
@@ -9076,7 +9800,9 @@
       <c r="B183" t="n">
         <v>0.227</v>
       </c>
-      <c r="C183" t="inlineStr"/>
+      <c r="C183" t="n">
+        <v>0.199</v>
+      </c>
       <c r="D183" t="n">
         <v>41</v>
       </c>
@@ -9088,7 +9814,9 @@
       <c r="H183" t="n">
         <v>13</v>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="n">
+        <v>12</v>
+      </c>
       <c r="J183" t="n">
         <v>37</v>
       </c>
@@ -9123,7 +9851,9 @@
       <c r="B184" t="n">
         <v>0.179</v>
       </c>
-      <c r="C184" t="inlineStr"/>
+      <c r="C184" t="n">
+        <v>0.188</v>
+      </c>
       <c r="D184" t="n">
         <v>21</v>
       </c>
@@ -9135,7 +9865,9 @@
       <c r="H184" t="n">
         <v>13</v>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="n">
+        <v>12</v>
+      </c>
       <c r="J184" t="n">
         <v>39</v>
       </c>
@@ -9170,7 +9902,9 @@
       <c r="B185" t="n">
         <v>0.203</v>
       </c>
-      <c r="C185" t="inlineStr"/>
+      <c r="C185" t="n">
+        <v>0.212</v>
+      </c>
       <c r="D185" t="n">
         <v>26</v>
       </c>
@@ -9182,7 +9916,9 @@
       <c r="H185" t="n">
         <v>13</v>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="n">
+        <v>13</v>
+      </c>
       <c r="J185" t="n">
         <v>42</v>
       </c>
@@ -9217,7 +9953,9 @@
       <c r="B186" t="n">
         <v>0.249</v>
       </c>
-      <c r="C186" t="inlineStr"/>
+      <c r="C186" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D186" t="n">
         <v>46</v>
       </c>
@@ -9229,7 +9967,9 @@
       <c r="H186" t="n">
         <v>13</v>
       </c>
-      <c r="I186" t="inlineStr"/>
+      <c r="I186" t="n">
+        <v>14</v>
+      </c>
       <c r="J186" t="n">
         <v>43</v>
       </c>
@@ -9264,7 +10004,9 @@
       <c r="B187" t="n">
         <v>0.24</v>
       </c>
-      <c r="C187" t="inlineStr"/>
+      <c r="C187" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D187" t="n">
         <v>53</v>
       </c>
@@ -9276,7 +10018,9 @@
       <c r="H187" t="n">
         <v>13</v>
       </c>
-      <c r="I187" t="inlineStr"/>
+      <c r="I187" t="n">
+        <v>12</v>
+      </c>
       <c r="J187" t="n">
         <v>48</v>
       </c>
@@ -9311,7 +10055,9 @@
       <c r="B188" t="n">
         <v>0.284</v>
       </c>
-      <c r="C188" t="inlineStr"/>
+      <c r="C188" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D188" t="n">
         <v>67</v>
       </c>
@@ -9323,7 +10069,9 @@
       <c r="H188" t="n">
         <v>13</v>
       </c>
-      <c r="I188" t="inlineStr"/>
+      <c r="I188" t="n">
+        <v>15</v>
+      </c>
       <c r="J188" t="n">
         <v>65</v>
       </c>
@@ -9358,7 +10106,9 @@
       <c r="B189" t="n">
         <v>0.248</v>
       </c>
-      <c r="C189" t="inlineStr"/>
+      <c r="C189" t="n">
+        <v>0.244</v>
+      </c>
       <c r="D189" t="n">
         <v>42</v>
       </c>
@@ -9370,7 +10120,9 @@
       <c r="H189" t="n">
         <v>13</v>
       </c>
-      <c r="I189" t="inlineStr"/>
+      <c r="I189" t="n">
+        <v>13</v>
+      </c>
       <c r="J189" t="n">
         <v>49</v>
       </c>
@@ -9405,7 +10157,9 @@
       <c r="B190" t="n">
         <v>0.279</v>
       </c>
-      <c r="C190" t="inlineStr"/>
+      <c r="C190" t="n">
+        <v>0.277</v>
+      </c>
       <c r="D190" t="n">
         <v>33</v>
       </c>
@@ -9417,7 +10171,9 @@
       <c r="H190" t="n">
         <v>13</v>
       </c>
-      <c r="I190" t="inlineStr"/>
+      <c r="I190" t="n">
+        <v>10</v>
+      </c>
       <c r="J190" t="n">
         <v>59</v>
       </c>
@@ -9452,7 +10208,9 @@
       <c r="B191" t="n">
         <v>0.283</v>
       </c>
-      <c r="C191" t="inlineStr"/>
+      <c r="C191" t="n">
+        <v>0.306</v>
+      </c>
       <c r="D191" t="n">
         <v>51</v>
       </c>
@@ -9464,7 +10222,9 @@
       <c r="H191" t="n">
         <v>13</v>
       </c>
-      <c r="I191" t="inlineStr"/>
+      <c r="I191" t="n">
+        <v>13</v>
+      </c>
       <c r="J191" t="n">
         <v>44</v>
       </c>
@@ -9499,7 +10259,9 @@
       <c r="B192" t="n">
         <v>0.241</v>
       </c>
-      <c r="C192" t="inlineStr"/>
+      <c r="C192" t="n">
+        <v>0.249</v>
+      </c>
       <c r="D192" t="n">
         <v>63</v>
       </c>
@@ -9511,7 +10273,9 @@
       <c r="H192" t="n">
         <v>13</v>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="n">
+        <v>14</v>
+      </c>
       <c r="J192" t="n">
         <v>54</v>
       </c>
@@ -9546,7 +10310,9 @@
       <c r="B193" t="n">
         <v>0.226</v>
       </c>
-      <c r="C193" t="inlineStr"/>
+      <c r="C193" t="n">
+        <v>0.245</v>
+      </c>
       <c r="D193" t="n">
         <v>40</v>
       </c>
@@ -9558,7 +10324,9 @@
       <c r="H193" t="n">
         <v>13</v>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="n">
+        <v>10</v>
+      </c>
       <c r="J193" t="n">
         <v>43</v>
       </c>
@@ -9593,7 +10361,9 @@
       <c r="B194" t="n">
         <v>0.294</v>
       </c>
-      <c r="C194" t="inlineStr"/>
+      <c r="C194" t="n">
+        <v>0.303</v>
+      </c>
       <c r="D194" t="n">
         <v>48</v>
       </c>
@@ -9605,7 +10375,9 @@
       <c r="H194" t="n">
         <v>12</v>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="n">
+        <v>14</v>
+      </c>
       <c r="J194" t="n">
         <v>52</v>
       </c>
@@ -9640,7 +10412,9 @@
       <c r="B195" t="n">
         <v>0.231</v>
       </c>
-      <c r="C195" t="inlineStr"/>
+      <c r="C195" t="n">
+        <v>0.238</v>
+      </c>
       <c r="D195" t="n">
         <v>40</v>
       </c>
@@ -9652,7 +10426,9 @@
       <c r="H195" t="n">
         <v>12</v>
       </c>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="n">
+        <v>12</v>
+      </c>
       <c r="J195" t="n">
         <v>40</v>
       </c>
@@ -9687,7 +10463,9 @@
       <c r="B196" t="n">
         <v>0.232</v>
       </c>
-      <c r="C196" t="inlineStr"/>
+      <c r="C196" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D196" t="n">
         <v>48</v>
       </c>
@@ -9699,7 +10477,9 @@
       <c r="H196" t="n">
         <v>12</v>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="n">
+        <v>11</v>
+      </c>
       <c r="J196" t="n">
         <v>42</v>
       </c>
@@ -9734,7 +10514,9 @@
       <c r="B197" t="n">
         <v>0.266</v>
       </c>
-      <c r="C197" t="inlineStr"/>
+      <c r="C197" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D197" t="n">
         <v>52</v>
       </c>
@@ -9746,7 +10528,9 @@
       <c r="H197" t="n">
         <v>12</v>
       </c>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
       <c r="J197" t="n">
         <v>48</v>
       </c>
@@ -9781,7 +10565,9 @@
       <c r="B198" t="n">
         <v>0.241</v>
       </c>
-      <c r="C198" t="inlineStr"/>
+      <c r="C198" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D198" t="n">
         <v>47</v>
       </c>
@@ -9793,7 +10579,9 @@
       <c r="H198" t="n">
         <v>12</v>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="n">
+        <v>12</v>
+      </c>
       <c r="J198" t="n">
         <v>50</v>
       </c>
@@ -9828,7 +10616,9 @@
       <c r="B199" t="n">
         <v>0.241</v>
       </c>
-      <c r="C199" t="inlineStr"/>
+      <c r="C199" t="n">
+        <v>0.214</v>
+      </c>
       <c r="D199" t="n">
         <v>51</v>
       </c>
@@ -9840,7 +10630,9 @@
       <c r="H199" t="n">
         <v>12</v>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="n">
+        <v>12</v>
+      </c>
       <c r="J199" t="n">
         <v>43</v>
       </c>
@@ -9875,7 +10667,9 @@
       <c r="B200" t="n">
         <v>0.328</v>
       </c>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="n">
+        <v>0.35</v>
+      </c>
       <c r="D200" t="n">
         <v>68</v>
       </c>
@@ -9887,7 +10681,9 @@
       <c r="H200" t="n">
         <v>12</v>
       </c>
-      <c r="I200" t="inlineStr"/>
+      <c r="I200" t="n">
+        <v>13</v>
+      </c>
       <c r="J200" t="n">
         <v>51</v>
       </c>
@@ -9922,7 +10718,9 @@
       <c r="B201" t="n">
         <v>0.187</v>
       </c>
-      <c r="C201" t="inlineStr"/>
+      <c r="C201" t="n">
+        <v>0.186</v>
+      </c>
       <c r="D201" t="n">
         <v>24</v>
       </c>
@@ -9934,7 +10732,9 @@
       <c r="H201" t="n">
         <v>12</v>
       </c>
-      <c r="I201" t="inlineStr"/>
+      <c r="I201" t="n">
+        <v>10</v>
+      </c>
       <c r="J201" t="n">
         <v>29</v>
       </c>
@@ -9969,7 +10769,9 @@
       <c r="B202" t="n">
         <v>0.232</v>
       </c>
-      <c r="C202" t="inlineStr"/>
+      <c r="C202" t="n">
+        <v>0.192</v>
+      </c>
       <c r="D202" t="n">
         <v>42</v>
       </c>
@@ -9981,7 +10783,9 @@
       <c r="H202" t="n">
         <v>11</v>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
       <c r="J202" t="n">
         <v>34</v>
       </c>
@@ -10016,7 +10820,9 @@
       <c r="B203" t="n">
         <v>0.239</v>
       </c>
-      <c r="C203" t="inlineStr"/>
+      <c r="C203" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D203" t="n">
         <v>67</v>
       </c>
@@ -10028,7 +10834,9 @@
       <c r="H203" t="n">
         <v>11</v>
       </c>
-      <c r="I203" t="inlineStr"/>
+      <c r="I203" t="n">
+        <v>12</v>
+      </c>
       <c r="J203" t="n">
         <v>60</v>
       </c>
@@ -10063,7 +10871,9 @@
       <c r="B204" t="n">
         <v>0.219</v>
       </c>
-      <c r="C204" t="inlineStr"/>
+      <c r="C204" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D204" t="n">
         <v>38</v>
       </c>
@@ -10075,7 +10885,9 @@
       <c r="H204" t="n">
         <v>11</v>
       </c>
-      <c r="I204" t="inlineStr"/>
+      <c r="I204" t="n">
+        <v>11</v>
+      </c>
       <c r="J204" t="n">
         <v>40</v>
       </c>
@@ -10110,7 +10922,9 @@
       <c r="B205" t="n">
         <v>0.232</v>
       </c>
-      <c r="C205" t="inlineStr"/>
+      <c r="C205" t="n">
+        <v>0.22</v>
+      </c>
       <c r="D205" t="n">
         <v>23</v>
       </c>
@@ -10122,7 +10936,9 @@
       <c r="H205" t="n">
         <v>11</v>
       </c>
-      <c r="I205" t="inlineStr"/>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
       <c r="J205" t="n">
         <v>52</v>
       </c>
@@ -10157,7 +10973,9 @@
       <c r="B206" t="n">
         <v>0.253</v>
       </c>
-      <c r="C206" t="inlineStr"/>
+      <c r="C206" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D206" t="n">
         <v>43</v>
       </c>
@@ -10169,7 +10987,9 @@
       <c r="H206" t="n">
         <v>11</v>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="n">
+        <v>10</v>
+      </c>
       <c r="J206" t="n">
         <v>49</v>
       </c>
@@ -10204,7 +11024,9 @@
       <c r="B207" t="n">
         <v>0.258</v>
       </c>
-      <c r="C207" t="inlineStr"/>
+      <c r="C207" t="n">
+        <v>0.249</v>
+      </c>
       <c r="D207" t="n">
         <v>49</v>
       </c>
@@ -10216,7 +11038,9 @@
       <c r="H207" t="n">
         <v>11</v>
       </c>
-      <c r="I207" t="inlineStr"/>
+      <c r="I207" t="n">
+        <v>12</v>
+      </c>
       <c r="J207" t="n">
         <v>45</v>
       </c>
@@ -10251,7 +11075,9 @@
       <c r="B208" t="n">
         <v>0.277</v>
       </c>
-      <c r="C208" t="inlineStr"/>
+      <c r="C208" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D208" t="n">
         <v>45</v>
       </c>
@@ -10263,7 +11089,9 @@
       <c r="H208" t="n">
         <v>11</v>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="n">
+        <v>12</v>
+      </c>
       <c r="J208" t="n">
         <v>51</v>
       </c>
@@ -10298,7 +11126,9 @@
       <c r="B209" t="n">
         <v>0.238</v>
       </c>
-      <c r="C209" t="inlineStr"/>
+      <c r="C209" t="n">
+        <v>0.217</v>
+      </c>
       <c r="D209" t="n">
         <v>42</v>
       </c>
@@ -10310,7 +11140,9 @@
       <c r="H209" t="n">
         <v>11</v>
       </c>
-      <c r="I209" t="inlineStr"/>
+      <c r="I209" t="n">
+        <v>11</v>
+      </c>
       <c r="J209" t="n">
         <v>40</v>
       </c>
@@ -10345,7 +11177,9 @@
       <c r="B210" t="n">
         <v>0.291</v>
       </c>
-      <c r="C210" t="inlineStr"/>
+      <c r="C210" t="n">
+        <v>0.296</v>
+      </c>
       <c r="D210" t="n">
         <v>62</v>
       </c>
@@ -10357,7 +11191,9 @@
       <c r="H210" t="n">
         <v>11</v>
       </c>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="n">
+        <v>13</v>
+      </c>
       <c r="J210" t="n">
         <v>51</v>
       </c>
@@ -10392,7 +11228,9 @@
       <c r="B211" t="n">
         <v>0.275</v>
       </c>
-      <c r="C211" t="inlineStr"/>
+      <c r="C211" t="n">
+        <v>0.274</v>
+      </c>
       <c r="D211" t="n">
         <v>62</v>
       </c>
@@ -10404,7 +11242,9 @@
       <c r="H211" t="n">
         <v>11</v>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
       <c r="J211" t="n">
         <v>55</v>
       </c>
@@ -10439,7 +11279,9 @@
       <c r="B212" t="n">
         <v>0.208</v>
       </c>
-      <c r="C212" t="inlineStr"/>
+      <c r="C212" t="n">
+        <v>0.22</v>
+      </c>
       <c r="D212" t="n">
         <v>28</v>
       </c>
@@ -10451,7 +11293,9 @@
       <c r="H212" t="n">
         <v>11</v>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="n">
+        <v>11</v>
+      </c>
       <c r="J212" t="n">
         <v>32</v>
       </c>
@@ -10486,7 +11330,9 @@
       <c r="B213" t="n">
         <v>0.237</v>
       </c>
-      <c r="C213" t="inlineStr"/>
+      <c r="C213" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D213" t="n">
         <v>51</v>
       </c>
@@ -10498,7 +11344,9 @@
       <c r="H213" t="n">
         <v>11</v>
       </c>
-      <c r="I213" t="inlineStr"/>
+      <c r="I213" t="n">
+        <v>12</v>
+      </c>
       <c r="J213" t="n">
         <v>43</v>
       </c>
@@ -10533,7 +11381,9 @@
       <c r="B214" t="n">
         <v>0.269</v>
       </c>
-      <c r="C214" t="inlineStr"/>
+      <c r="C214" t="n">
+        <v>0.274</v>
+      </c>
       <c r="D214" t="n">
         <v>45</v>
       </c>
@@ -10545,7 +11395,9 @@
       <c r="H214" t="n">
         <v>11</v>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="n">
+        <v>8</v>
+      </c>
       <c r="J214" t="n">
         <v>46</v>
       </c>
@@ -10580,7 +11432,9 @@
       <c r="B215" t="n">
         <v>0.289</v>
       </c>
-      <c r="C215" t="inlineStr"/>
+      <c r="C215" t="n">
+        <v>0.276</v>
+      </c>
       <c r="D215" t="n">
         <v>62</v>
       </c>
@@ -10592,7 +11446,9 @@
       <c r="H215" t="n">
         <v>10</v>
       </c>
-      <c r="I215" t="inlineStr"/>
+      <c r="I215" t="n">
+        <v>11</v>
+      </c>
       <c r="J215" t="n">
         <v>50</v>
       </c>
@@ -10627,7 +11483,9 @@
       <c r="B216" t="n">
         <v>0.298</v>
       </c>
-      <c r="C216" t="inlineStr"/>
+      <c r="C216" t="n">
+        <v>0.244</v>
+      </c>
       <c r="D216" t="n">
         <v>53</v>
       </c>
@@ -10639,7 +11497,9 @@
       <c r="H216" t="n">
         <v>10</v>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="n">
+        <v>11</v>
+      </c>
       <c r="J216" t="n">
         <v>49</v>
       </c>
@@ -10674,7 +11534,9 @@
       <c r="B217" t="n">
         <v>0.264</v>
       </c>
-      <c r="C217" t="inlineStr"/>
+      <c r="C217" t="n">
+        <v>0.221</v>
+      </c>
       <c r="D217" t="n">
         <v>50</v>
       </c>
@@ -10686,7 +11548,9 @@
       <c r="H217" t="n">
         <v>10</v>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
       <c r="J217" t="n">
         <v>48</v>
       </c>
@@ -10721,7 +11585,9 @@
       <c r="B218" t="n">
         <v>0.226</v>
       </c>
-      <c r="C218" t="inlineStr"/>
+      <c r="C218" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D218" t="n">
         <v>31</v>
       </c>
@@ -10733,7 +11599,9 @@
       <c r="H218" t="n">
         <v>10</v>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="n">
+        <v>10</v>
+      </c>
       <c r="J218" t="n">
         <v>33</v>
       </c>
@@ -10768,7 +11636,9 @@
       <c r="B219" t="n">
         <v>0.227</v>
       </c>
-      <c r="C219" t="inlineStr"/>
+      <c r="C219" t="n">
+        <v>0.235</v>
+      </c>
       <c r="D219" t="n">
         <v>37</v>
       </c>
@@ -10780,7 +11650,9 @@
       <c r="H219" t="n">
         <v>10</v>
       </c>
-      <c r="I219" t="inlineStr"/>
+      <c r="I219" t="n">
+        <v>8</v>
+      </c>
       <c r="J219" t="n">
         <v>32</v>
       </c>
@@ -10815,7 +11687,9 @@
       <c r="B220" t="n">
         <v>0.256</v>
       </c>
-      <c r="C220" t="inlineStr"/>
+      <c r="C220" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D220" t="n">
         <v>45</v>
       </c>
@@ -10827,7 +11701,9 @@
       <c r="H220" t="n">
         <v>10</v>
       </c>
-      <c r="I220" t="inlineStr"/>
+      <c r="I220" t="n">
+        <v>11</v>
+      </c>
       <c r="J220" t="n">
         <v>44</v>
       </c>
@@ -10862,7 +11738,9 @@
       <c r="B221" t="n">
         <v>0.268</v>
       </c>
-      <c r="C221" t="inlineStr"/>
+      <c r="C221" t="n">
+        <v>0.287</v>
+      </c>
       <c r="D221" t="n">
         <v>55</v>
       </c>
@@ -10874,7 +11752,9 @@
       <c r="H221" t="n">
         <v>10</v>
       </c>
-      <c r="I221" t="inlineStr"/>
+      <c r="I221" t="n">
+        <v>10</v>
+      </c>
       <c r="J221" t="n">
         <v>45</v>
       </c>
@@ -10909,7 +11789,9 @@
       <c r="B222" t="n">
         <v>0.317</v>
       </c>
-      <c r="C222" t="inlineStr"/>
+      <c r="C222" t="n">
+        <v>0.303</v>
+      </c>
       <c r="D222" t="n">
         <v>67</v>
       </c>
@@ -10921,7 +11803,9 @@
       <c r="H222" t="n">
         <v>10</v>
       </c>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="n">
+        <v>9</v>
+      </c>
       <c r="J222" t="n">
         <v>57</v>
       </c>
@@ -10956,7 +11840,9 @@
       <c r="B223" t="n">
         <v>0.24</v>
       </c>
-      <c r="C223" t="inlineStr"/>
+      <c r="C223" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D223" t="n">
         <v>56</v>
       </c>
@@ -10968,7 +11854,9 @@
       <c r="H223" t="n">
         <v>10</v>
       </c>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="n">
+        <v>8</v>
+      </c>
       <c r="J223" t="n">
         <v>34</v>
       </c>
@@ -11003,7 +11891,9 @@
       <c r="B224" t="n">
         <v>0.298</v>
       </c>
-      <c r="C224" t="inlineStr"/>
+      <c r="C224" t="n">
+        <v>0.294</v>
+      </c>
       <c r="D224" t="n">
         <v>61</v>
       </c>
@@ -11015,7 +11905,9 @@
       <c r="H224" t="n">
         <v>10</v>
       </c>
-      <c r="I224" t="inlineStr"/>
+      <c r="I224" t="n">
+        <v>10</v>
+      </c>
       <c r="J224" t="n">
         <v>58</v>
       </c>
@@ -11050,7 +11942,9 @@
       <c r="B225" t="n">
         <v>0.215</v>
       </c>
-      <c r="C225" t="inlineStr"/>
+      <c r="C225" t="n">
+        <v>0.217</v>
+      </c>
       <c r="D225" t="n">
         <v>37</v>
       </c>
@@ -11062,7 +11956,9 @@
       <c r="H225" t="n">
         <v>10</v>
       </c>
-      <c r="I225" t="inlineStr"/>
+      <c r="I225" t="n">
+        <v>9</v>
+      </c>
       <c r="J225" t="n">
         <v>35</v>
       </c>
@@ -11097,7 +11993,9 @@
       <c r="B226" t="n">
         <v>0.279</v>
       </c>
-      <c r="C226" t="inlineStr"/>
+      <c r="C226" t="n">
+        <v>0.289</v>
+      </c>
       <c r="D226" t="n">
         <v>52</v>
       </c>
@@ -11109,7 +12007,9 @@
       <c r="H226" t="n">
         <v>10</v>
       </c>
-      <c r="I226" t="inlineStr"/>
+      <c r="I226" t="n">
+        <v>10</v>
+      </c>
       <c r="J226" t="n">
         <v>62</v>
       </c>
@@ -11144,7 +12044,9 @@
       <c r="B227" t="n">
         <v>0.284</v>
       </c>
-      <c r="C227" t="inlineStr"/>
+      <c r="C227" t="n">
+        <v>0.269</v>
+      </c>
       <c r="D227" t="n">
         <v>56</v>
       </c>
@@ -11156,7 +12058,9 @@
       <c r="H227" t="n">
         <v>10</v>
       </c>
-      <c r="I227" t="inlineStr"/>
+      <c r="I227" t="n">
+        <v>9</v>
+      </c>
       <c r="J227" t="n">
         <v>50</v>
       </c>
@@ -11191,7 +12095,9 @@
       <c r="B228" t="n">
         <v>0.213</v>
       </c>
-      <c r="C228" t="inlineStr"/>
+      <c r="C228" t="n">
+        <v>0.208</v>
+      </c>
       <c r="D228" t="n">
         <v>39</v>
       </c>
@@ -11203,7 +12109,9 @@
       <c r="H228" t="n">
         <v>10</v>
       </c>
-      <c r="I228" t="inlineStr"/>
+      <c r="I228" t="n">
+        <v>11</v>
+      </c>
       <c r="J228" t="n">
         <v>35</v>
       </c>
@@ -11238,7 +12146,9 @@
       <c r="B229" t="n">
         <v>0.25</v>
       </c>
-      <c r="C229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D229" t="n">
         <v>34</v>
       </c>
@@ -11250,7 +12160,9 @@
       <c r="H229" t="n">
         <v>10</v>
       </c>
-      <c r="I229" t="inlineStr"/>
+      <c r="I229" t="n">
+        <v>9</v>
+      </c>
       <c r="J229" t="n">
         <v>49</v>
       </c>
@@ -11285,7 +12197,9 @@
       <c r="B230" t="n">
         <v>0.226</v>
       </c>
-      <c r="C230" t="inlineStr"/>
+      <c r="C230" t="n">
+        <v>0.219</v>
+      </c>
       <c r="D230" t="n">
         <v>29</v>
       </c>
@@ -11297,7 +12211,9 @@
       <c r="H230" t="n">
         <v>10</v>
       </c>
-      <c r="I230" t="inlineStr"/>
+      <c r="I230" t="n">
+        <v>9</v>
+      </c>
       <c r="J230" t="n">
         <v>35</v>
       </c>
@@ -11332,7 +12248,9 @@
       <c r="B231" t="n">
         <v>0.289</v>
       </c>
-      <c r="C231" t="inlineStr"/>
+      <c r="C231" t="n">
+        <v>0.304</v>
+      </c>
       <c r="D231" t="n">
         <v>80</v>
       </c>
@@ -11344,7 +12262,9 @@
       <c r="H231" t="n">
         <v>10</v>
       </c>
-      <c r="I231" t="inlineStr"/>
+      <c r="I231" t="n">
+        <v>11</v>
+      </c>
       <c r="J231" t="n">
         <v>55</v>
       </c>
@@ -11379,7 +12299,9 @@
       <c r="B232" t="n">
         <v>0.287</v>
       </c>
-      <c r="C232" t="inlineStr"/>
+      <c r="C232" t="n">
+        <v>0.296</v>
+      </c>
       <c r="D232" t="n">
         <v>72</v>
       </c>
@@ -11391,7 +12313,9 @@
       <c r="H232" t="n">
         <v>10</v>
       </c>
-      <c r="I232" t="inlineStr"/>
+      <c r="I232" t="n">
+        <v>10</v>
+      </c>
       <c r="J232" t="n">
         <v>59</v>
       </c>
@@ -11426,7 +12350,9 @@
       <c r="B233" t="n">
         <v>0.183</v>
       </c>
-      <c r="C233" t="inlineStr"/>
+      <c r="C233" t="n">
+        <v>0.186</v>
+      </c>
       <c r="D233" t="n">
         <v>25</v>
       </c>
@@ -11438,7 +12364,9 @@
       <c r="H233" t="n">
         <v>10</v>
       </c>
-      <c r="I233" t="inlineStr"/>
+      <c r="I233" t="n">
+        <v>9</v>
+      </c>
       <c r="J233" t="n">
         <v>26</v>
       </c>
@@ -11473,7 +12401,9 @@
       <c r="B234" t="n">
         <v>0.221</v>
       </c>
-      <c r="C234" t="inlineStr"/>
+      <c r="C234" t="n">
+        <v>0.223</v>
+      </c>
       <c r="D234" t="n">
         <v>26</v>
       </c>
@@ -11485,7 +12415,9 @@
       <c r="H234" t="n">
         <v>10</v>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="n">
+        <v>9</v>
+      </c>
       <c r="J234" t="n">
         <v>38</v>
       </c>
@@ -11520,7 +12452,9 @@
       <c r="B235" t="n">
         <v>0.234</v>
       </c>
-      <c r="C235" t="inlineStr"/>
+      <c r="C235" t="n">
+        <v>0.245</v>
+      </c>
       <c r="D235" t="n">
         <v>52</v>
       </c>
@@ -11532,7 +12466,9 @@
       <c r="H235" t="n">
         <v>10</v>
       </c>
-      <c r="I235" t="inlineStr"/>
+      <c r="I235" t="n">
+        <v>11</v>
+      </c>
       <c r="J235" t="n">
         <v>45</v>
       </c>
@@ -11567,7 +12503,9 @@
       <c r="B236" t="n">
         <v>0.242</v>
       </c>
-      <c r="C236" t="inlineStr"/>
+      <c r="C236" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D236" t="n">
         <v>41</v>
       </c>
@@ -11579,7 +12517,9 @@
       <c r="H236" t="n">
         <v>10</v>
       </c>
-      <c r="I236" t="inlineStr"/>
+      <c r="I236" t="n">
+        <v>9</v>
+      </c>
       <c r="J236" t="n">
         <v>37</v>
       </c>
@@ -11614,7 +12554,9 @@
       <c r="B237" t="n">
         <v>0.243</v>
       </c>
-      <c r="C237" t="inlineStr"/>
+      <c r="C237" t="n">
+        <v>0.254</v>
+      </c>
       <c r="D237" t="n">
         <v>47</v>
       </c>
@@ -11626,7 +12568,9 @@
       <c r="H237" t="n">
         <v>10</v>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="n">
+        <v>10</v>
+      </c>
       <c r="J237" t="n">
         <v>44</v>
       </c>
@@ -11661,7 +12605,9 @@
       <c r="B238" t="n">
         <v>0.227</v>
       </c>
-      <c r="C238" t="inlineStr"/>
+      <c r="C238" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D238" t="n">
         <v>28</v>
       </c>
@@ -11673,7 +12619,9 @@
       <c r="H238" t="n">
         <v>10</v>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>12</v>
+      </c>
       <c r="J238" t="n">
         <v>39</v>
       </c>
@@ -11708,7 +12656,9 @@
       <c r="B239" t="n">
         <v>0.218</v>
       </c>
-      <c r="C239" t="inlineStr"/>
+      <c r="C239" t="n">
+        <v>0.2</v>
+      </c>
       <c r="D239" t="n">
         <v>41</v>
       </c>
@@ -11720,7 +12670,9 @@
       <c r="H239" t="n">
         <v>9</v>
       </c>
-      <c r="I239" t="inlineStr"/>
+      <c r="I239" t="n">
+        <v>8</v>
+      </c>
       <c r="J239" t="n">
         <v>32</v>
       </c>
@@ -11755,7 +12707,9 @@
       <c r="B240" t="n">
         <v>0.276</v>
       </c>
-      <c r="C240" t="inlineStr"/>
+      <c r="C240" t="n">
+        <v>0.28</v>
+      </c>
       <c r="D240" t="n">
         <v>39</v>
       </c>
@@ -11767,7 +12721,9 @@
       <c r="H240" t="n">
         <v>9</v>
       </c>
-      <c r="I240" t="inlineStr"/>
+      <c r="I240" t="n">
+        <v>9</v>
+      </c>
       <c r="J240" t="n">
         <v>32</v>
       </c>
@@ -11802,7 +12758,9 @@
       <c r="B241" t="n">
         <v>0.251</v>
       </c>
-      <c r="C241" t="inlineStr"/>
+      <c r="C241" t="n">
+        <v>0.205</v>
+      </c>
       <c r="D241" t="n">
         <v>40</v>
       </c>
@@ -11814,7 +12772,9 @@
       <c r="H241" t="n">
         <v>9</v>
       </c>
-      <c r="I241" t="inlineStr"/>
+      <c r="I241" t="n">
+        <v>7</v>
+      </c>
       <c r="J241" t="n">
         <v>33</v>
       </c>
@@ -11849,7 +12809,9 @@
       <c r="B242" t="n">
         <v>0.254</v>
       </c>
-      <c r="C242" t="inlineStr"/>
+      <c r="C242" t="n">
+        <v>0.263</v>
+      </c>
       <c r="D242" t="n">
         <v>45</v>
       </c>
@@ -11861,7 +12823,9 @@
       <c r="H242" t="n">
         <v>9</v>
       </c>
-      <c r="I242" t="inlineStr"/>
+      <c r="I242" t="n">
+        <v>9</v>
+      </c>
       <c r="J242" t="n">
         <v>50</v>
       </c>
@@ -11896,7 +12860,9 @@
       <c r="B243" t="n">
         <v>0.19</v>
       </c>
-      <c r="C243" t="inlineStr"/>
+      <c r="C243" t="n">
+        <v>0.192</v>
+      </c>
       <c r="D243" t="n">
         <v>20</v>
       </c>
@@ -11908,7 +12874,9 @@
       <c r="H243" t="n">
         <v>9</v>
       </c>
-      <c r="I243" t="inlineStr"/>
+      <c r="I243" t="n">
+        <v>8</v>
+      </c>
       <c r="J243" t="n">
         <v>32</v>
       </c>
@@ -11943,7 +12911,9 @@
       <c r="B244" t="n">
         <v>0.255</v>
       </c>
-      <c r="C244" t="inlineStr"/>
+      <c r="C244" t="n">
+        <v>0.265</v>
+      </c>
       <c r="D244" t="n">
         <v>59</v>
       </c>
@@ -11955,7 +12925,9 @@
       <c r="H244" t="n">
         <v>9</v>
       </c>
-      <c r="I244" t="inlineStr"/>
+      <c r="I244" t="n">
+        <v>9</v>
+      </c>
       <c r="J244" t="n">
         <v>46</v>
       </c>
@@ -11990,7 +12962,9 @@
       <c r="B245" t="n">
         <v>0.255</v>
       </c>
-      <c r="C245" t="inlineStr"/>
+      <c r="C245" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D245" t="n">
         <v>57</v>
       </c>
@@ -12002,7 +12976,9 @@
       <c r="H245" t="n">
         <v>9</v>
       </c>
-      <c r="I245" t="inlineStr"/>
+      <c r="I245" t="n">
+        <v>9</v>
+      </c>
       <c r="J245" t="n">
         <v>47</v>
       </c>
@@ -12037,7 +13013,9 @@
       <c r="B246" t="n">
         <v>0.232</v>
       </c>
-      <c r="C246" t="inlineStr"/>
+      <c r="C246" t="n">
+        <v>0.224</v>
+      </c>
       <c r="D246" t="n">
         <v>31</v>
       </c>
@@ -12049,7 +13027,9 @@
       <c r="H246" t="n">
         <v>9</v>
       </c>
-      <c r="I246" t="inlineStr"/>
+      <c r="I246" t="n">
+        <v>10</v>
+      </c>
       <c r="J246" t="n">
         <v>39</v>
       </c>
@@ -12084,7 +13064,9 @@
       <c r="B247" t="n">
         <v>0.304</v>
       </c>
-      <c r="C247" t="inlineStr"/>
+      <c r="C247" t="n">
+        <v>0.306</v>
+      </c>
       <c r="D247" t="n">
         <v>33</v>
       </c>
@@ -12096,7 +13078,9 @@
       <c r="H247" t="n">
         <v>9</v>
       </c>
-      <c r="I247" t="inlineStr"/>
+      <c r="I247" t="n">
+        <v>7</v>
+      </c>
       <c r="J247" t="n">
         <v>36</v>
       </c>
@@ -12131,7 +13115,9 @@
       <c r="B248" t="n">
         <v>0.265</v>
       </c>
-      <c r="C248" t="inlineStr"/>
+      <c r="C248" t="n">
+        <v>0.229</v>
+      </c>
       <c r="D248" t="n">
         <v>50</v>
       </c>
@@ -12143,7 +13129,9 @@
       <c r="H248" t="n">
         <v>9</v>
       </c>
-      <c r="I248" t="inlineStr"/>
+      <c r="I248" t="n">
+        <v>8</v>
+      </c>
       <c r="J248" t="n">
         <v>43</v>
       </c>
@@ -12178,7 +13166,9 @@
       <c r="B249" t="n">
         <v>0.236</v>
       </c>
-      <c r="C249" t="inlineStr"/>
+      <c r="C249" t="n">
+        <v>0.239</v>
+      </c>
       <c r="D249" t="n">
         <v>32</v>
       </c>
@@ -12190,7 +13180,9 @@
       <c r="H249" t="n">
         <v>9</v>
       </c>
-      <c r="I249" t="inlineStr"/>
+      <c r="I249" t="n">
+        <v>7</v>
+      </c>
       <c r="J249" t="n">
         <v>34</v>
       </c>
@@ -12225,7 +13217,9 @@
       <c r="B250" t="n">
         <v>0.237</v>
       </c>
-      <c r="C250" t="inlineStr"/>
+      <c r="C250" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D250" t="n">
         <v>42</v>
       </c>
@@ -12237,7 +13231,9 @@
       <c r="H250" t="n">
         <v>9</v>
       </c>
-      <c r="I250" t="inlineStr"/>
+      <c r="I250" t="n">
+        <v>8</v>
+      </c>
       <c r="J250" t="n">
         <v>31</v>
       </c>
@@ -12272,7 +13268,9 @@
       <c r="B251" t="n">
         <v>0.256</v>
       </c>
-      <c r="C251" t="inlineStr"/>
+      <c r="C251" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D251" t="n">
         <v>58</v>
       </c>
@@ -12284,7 +13282,9 @@
       <c r="H251" t="n">
         <v>9</v>
       </c>
-      <c r="I251" t="inlineStr"/>
+      <c r="I251" t="n">
+        <v>7</v>
+      </c>
       <c r="J251" t="n">
         <v>45</v>
       </c>
@@ -12319,7 +13319,9 @@
       <c r="B252" t="n">
         <v>0.243</v>
       </c>
-      <c r="C252" t="inlineStr"/>
+      <c r="C252" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D252" t="n">
         <v>46</v>
       </c>
@@ -12331,7 +13333,9 @@
       <c r="H252" t="n">
         <v>9</v>
       </c>
-      <c r="I252" t="inlineStr"/>
+      <c r="I252" t="n">
+        <v>8</v>
+      </c>
       <c r="J252" t="n">
         <v>36</v>
       </c>
@@ -12366,7 +13370,9 @@
       <c r="B253" t="n">
         <v>0.234</v>
       </c>
-      <c r="C253" t="inlineStr"/>
+      <c r="C253" t="n">
+        <v>0.256</v>
+      </c>
       <c r="D253" t="n">
         <v>38</v>
       </c>
@@ -12378,7 +13384,9 @@
       <c r="H253" t="n">
         <v>9</v>
       </c>
-      <c r="I253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>8</v>
+      </c>
       <c r="J253" t="n">
         <v>39</v>
       </c>
@@ -12413,7 +13421,9 @@
       <c r="B254" t="n">
         <v>0.244</v>
       </c>
-      <c r="C254" t="inlineStr"/>
+      <c r="C254" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D254" t="n">
         <v>35</v>
       </c>
@@ -12425,7 +13435,9 @@
       <c r="H254" t="n">
         <v>9</v>
       </c>
-      <c r="I254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>7</v>
+      </c>
       <c r="J254" t="n">
         <v>34</v>
       </c>
@@ -12460,7 +13472,9 @@
       <c r="B255" t="n">
         <v>0.257</v>
       </c>
-      <c r="C255" t="inlineStr"/>
+      <c r="C255" t="n">
+        <v>0.264</v>
+      </c>
       <c r="D255" t="n">
         <v>51</v>
       </c>
@@ -12472,7 +13486,9 @@
       <c r="H255" t="n">
         <v>9</v>
       </c>
-      <c r="I255" t="inlineStr"/>
+      <c r="I255" t="n">
+        <v>9</v>
+      </c>
       <c r="J255" t="n">
         <v>48</v>
       </c>
@@ -12507,7 +13523,9 @@
       <c r="B256" t="n">
         <v>0.22</v>
       </c>
-      <c r="C256" t="inlineStr"/>
+      <c r="C256" t="n">
+        <v>0.209</v>
+      </c>
       <c r="D256" t="n">
         <v>30</v>
       </c>
@@ -12519,7 +13537,9 @@
       <c r="H256" t="n">
         <v>9</v>
       </c>
-      <c r="I256" t="inlineStr"/>
+      <c r="I256" t="n">
+        <v>8</v>
+      </c>
       <c r="J256" t="n">
         <v>35</v>
       </c>
@@ -12554,7 +13574,9 @@
       <c r="B257" t="n">
         <v>0.303</v>
       </c>
-      <c r="C257" t="inlineStr"/>
+      <c r="C257" t="n">
+        <v>0.314</v>
+      </c>
       <c r="D257" t="n">
         <v>77</v>
       </c>
@@ -12566,7 +13588,9 @@
       <c r="H257" t="n">
         <v>8</v>
       </c>
-      <c r="I257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>8</v>
+      </c>
       <c r="J257" t="n">
         <v>42</v>
       </c>
@@ -12601,7 +13625,9 @@
       <c r="B258" t="n">
         <v>0.259</v>
       </c>
-      <c r="C258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>0.25</v>
+      </c>
       <c r="D258" t="n">
         <v>56</v>
       </c>
@@ -12613,7 +13639,9 @@
       <c r="H258" t="n">
         <v>8</v>
       </c>
-      <c r="I258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>9</v>
+      </c>
       <c r="J258" t="n">
         <v>38</v>
       </c>
@@ -12648,7 +13676,9 @@
       <c r="B259" t="n">
         <v>0.232</v>
       </c>
-      <c r="C259" t="inlineStr"/>
+      <c r="C259" t="n">
+        <v>0.228</v>
+      </c>
       <c r="D259" t="n">
         <v>51</v>
       </c>
@@ -12660,7 +13690,9 @@
       <c r="H259" t="n">
         <v>8</v>
       </c>
-      <c r="I259" t="inlineStr"/>
+      <c r="I259" t="n">
+        <v>7</v>
+      </c>
       <c r="J259" t="n">
         <v>35</v>
       </c>
@@ -12695,7 +13727,9 @@
       <c r="B260" t="n">
         <v>0.226</v>
       </c>
-      <c r="C260" t="inlineStr"/>
+      <c r="C260" t="n">
+        <v>0.206</v>
+      </c>
       <c r="D260" t="n">
         <v>34</v>
       </c>
@@ -12707,7 +13741,9 @@
       <c r="H260" t="n">
         <v>8</v>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>7</v>
+      </c>
       <c r="J260" t="n">
         <v>28</v>
       </c>
@@ -12742,7 +13778,9 @@
       <c r="B261" t="n">
         <v>0.214</v>
       </c>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="n">
+        <v>0.171</v>
+      </c>
       <c r="D261" t="n">
         <v>33</v>
       </c>
@@ -12754,7 +13792,9 @@
       <c r="H261" t="n">
         <v>8</v>
       </c>
-      <c r="I261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>7</v>
+      </c>
       <c r="J261" t="n">
         <v>32</v>
       </c>
@@ -12789,7 +13829,9 @@
       <c r="B262" t="n">
         <v>0.258</v>
       </c>
-      <c r="C262" t="inlineStr"/>
+      <c r="C262" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D262" t="n">
         <v>30</v>
       </c>
@@ -12801,7 +13843,9 @@
       <c r="H262" t="n">
         <v>8</v>
       </c>
-      <c r="I262" t="inlineStr"/>
+      <c r="I262" t="n">
+        <v>6</v>
+      </c>
       <c r="J262" t="n">
         <v>33</v>
       </c>
@@ -12836,7 +13880,9 @@
       <c r="B263" t="n">
         <v>0.245</v>
       </c>
-      <c r="C263" t="inlineStr"/>
+      <c r="C263" t="n">
+        <v>0.217</v>
+      </c>
       <c r="D263" t="n">
         <v>43</v>
       </c>
@@ -12848,7 +13894,9 @@
       <c r="H263" t="n">
         <v>8</v>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>9</v>
+      </c>
       <c r="J263" t="n">
         <v>32</v>
       </c>
@@ -12883,7 +13931,9 @@
       <c r="B264" t="n">
         <v>0.228</v>
       </c>
-      <c r="C264" t="inlineStr"/>
+      <c r="C264" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D264" t="n">
         <v>46</v>
       </c>
@@ -12895,7 +13945,9 @@
       <c r="H264" t="n">
         <v>8</v>
       </c>
-      <c r="I264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>8</v>
+      </c>
       <c r="J264" t="n">
         <v>32</v>
       </c>
@@ -12930,7 +13982,9 @@
       <c r="B265" t="n">
         <v>0.226</v>
       </c>
-      <c r="C265" t="inlineStr"/>
+      <c r="C265" t="n">
+        <v>0.242</v>
+      </c>
       <c r="D265" t="n">
         <v>26</v>
       </c>
@@ -12942,7 +13996,9 @@
       <c r="H265" t="n">
         <v>8</v>
       </c>
-      <c r="I265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>7</v>
+      </c>
       <c r="J265" t="n">
         <v>27</v>
       </c>
@@ -12977,7 +14033,9 @@
       <c r="B266" t="n">
         <v>0.182</v>
       </c>
-      <c r="C266" t="inlineStr"/>
+      <c r="C266" t="n">
+        <v>0.172</v>
+      </c>
       <c r="D266" t="n">
         <v>25</v>
       </c>
@@ -12989,7 +14047,9 @@
       <c r="H266" t="n">
         <v>8</v>
       </c>
-      <c r="I266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>8</v>
+      </c>
       <c r="J266" t="n">
         <v>27</v>
       </c>
@@ -13024,7 +14084,9 @@
       <c r="B267" t="n">
         <v>0.225</v>
       </c>
-      <c r="C267" t="inlineStr"/>
+      <c r="C267" t="n">
+        <v>0.218</v>
+      </c>
       <c r="D267" t="n">
         <v>34</v>
       </c>
@@ -13036,7 +14098,9 @@
       <c r="H267" t="n">
         <v>8</v>
       </c>
-      <c r="I267" t="inlineStr"/>
+      <c r="I267" t="n">
+        <v>11</v>
+      </c>
       <c r="J267" t="n">
         <v>29</v>
       </c>
@@ -13071,7 +14135,9 @@
       <c r="B268" t="n">
         <v>0.175</v>
       </c>
-      <c r="C268" t="inlineStr"/>
+      <c r="C268" t="n">
+        <v>0.186</v>
+      </c>
       <c r="D268" t="n">
         <v>22</v>
       </c>
@@ -13083,7 +14149,9 @@
       <c r="H268" t="n">
         <v>8</v>
       </c>
-      <c r="I268" t="inlineStr"/>
+      <c r="I268" t="n">
+        <v>5</v>
+      </c>
       <c r="J268" t="n">
         <v>18</v>
       </c>
@@ -13118,7 +14186,9 @@
       <c r="B269" t="n">
         <v>0.262</v>
       </c>
-      <c r="C269" t="inlineStr"/>
+      <c r="C269" t="n">
+        <v>0.257</v>
+      </c>
       <c r="D269" t="n">
         <v>39</v>
       </c>
@@ -13130,7 +14200,9 @@
       <c r="H269" t="n">
         <v>8</v>
       </c>
-      <c r="I269" t="inlineStr"/>
+      <c r="I269" t="n">
+        <v>7</v>
+      </c>
       <c r="J269" t="n">
         <v>35</v>
       </c>
@@ -13165,7 +14237,9 @@
       <c r="B270" t="n">
         <v>0.242</v>
       </c>
-      <c r="C270" t="inlineStr"/>
+      <c r="C270" t="n">
+        <v>0.243</v>
+      </c>
       <c r="D270" t="n">
         <v>62</v>
       </c>
@@ -13177,7 +14251,9 @@
       <c r="H270" t="n">
         <v>8</v>
       </c>
-      <c r="I270" t="inlineStr"/>
+      <c r="I270" t="n">
+        <v>9</v>
+      </c>
       <c r="J270" t="n">
         <v>45</v>
       </c>
@@ -13212,7 +14288,9 @@
       <c r="B271" t="n">
         <v>0.241</v>
       </c>
-      <c r="C271" t="inlineStr"/>
+      <c r="C271" t="n">
+        <v>0.256</v>
+      </c>
       <c r="D271" t="n">
         <v>33</v>
       </c>
@@ -13224,7 +14302,9 @@
       <c r="H271" t="n">
         <v>8</v>
       </c>
-      <c r="I271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>7</v>
+      </c>
       <c r="J271" t="n">
         <v>32</v>
       </c>
@@ -13259,7 +14339,9 @@
       <c r="B272" t="n">
         <v>0.228</v>
       </c>
-      <c r="C272" t="inlineStr"/>
+      <c r="C272" t="n">
+        <v>0.238</v>
+      </c>
       <c r="D272" t="n">
         <v>51</v>
       </c>
@@ -13271,7 +14353,9 @@
       <c r="H272" t="n">
         <v>8</v>
       </c>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="n">
+        <v>11</v>
+      </c>
       <c r="J272" t="n">
         <v>43</v>
       </c>
@@ -13306,7 +14390,9 @@
       <c r="B273" t="n">
         <v>0.222</v>
       </c>
-      <c r="C273" t="inlineStr"/>
+      <c r="C273" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D273" t="n">
         <v>25</v>
       </c>
@@ -13318,7 +14404,9 @@
       <c r="H273" t="n">
         <v>8</v>
       </c>
-      <c r="I273" t="inlineStr"/>
+      <c r="I273" t="n">
+        <v>9</v>
+      </c>
       <c r="J273" t="n">
         <v>28</v>
       </c>
@@ -13353,7 +14441,9 @@
       <c r="B274" t="n">
         <v>0.218</v>
       </c>
-      <c r="C274" t="inlineStr"/>
+      <c r="C274" t="n">
+        <v>0.209</v>
+      </c>
       <c r="D274" t="n">
         <v>21</v>
       </c>
@@ -13365,7 +14455,9 @@
       <c r="H274" t="n">
         <v>8</v>
       </c>
-      <c r="I274" t="inlineStr"/>
+      <c r="I274" t="n">
+        <v>9</v>
+      </c>
       <c r="J274" t="n">
         <v>36</v>
       </c>
@@ -13400,7 +14492,9 @@
       <c r="B275" t="n">
         <v>0.177</v>
       </c>
-      <c r="C275" t="inlineStr"/>
+      <c r="C275" t="n">
+        <v>0.177</v>
+      </c>
       <c r="D275" t="n">
         <v>30</v>
       </c>
@@ -13412,7 +14506,9 @@
       <c r="H275" t="n">
         <v>8</v>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>8</v>
+      </c>
       <c r="J275" t="n">
         <v>29</v>
       </c>
@@ -13447,7 +14543,9 @@
       <c r="B276" t="n">
         <v>0.238</v>
       </c>
-      <c r="C276" t="inlineStr"/>
+      <c r="C276" t="n">
+        <v>0.248</v>
+      </c>
       <c r="D276" t="n">
         <v>55</v>
       </c>
@@ -13459,7 +14557,9 @@
       <c r="H276" t="n">
         <v>8</v>
       </c>
-      <c r="I276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>8</v>
+      </c>
       <c r="J276" t="n">
         <v>34</v>
       </c>
@@ -13494,7 +14594,9 @@
       <c r="B277" t="n">
         <v>0.195</v>
       </c>
-      <c r="C277" t="inlineStr"/>
+      <c r="C277" t="n">
+        <v>0.208</v>
+      </c>
       <c r="D277" t="n">
         <v>20</v>
       </c>
@@ -13506,7 +14608,9 @@
       <c r="H277" t="n">
         <v>8</v>
       </c>
-      <c r="I277" t="inlineStr"/>
+      <c r="I277" t="n">
+        <v>4</v>
+      </c>
       <c r="J277" t="n">
         <v>24</v>
       </c>
@@ -13541,7 +14645,9 @@
       <c r="B278" t="n">
         <v>0.197</v>
       </c>
-      <c r="C278" t="inlineStr"/>
+      <c r="C278" t="n">
+        <v>0.2</v>
+      </c>
       <c r="D278" t="n">
         <v>24</v>
       </c>
@@ -13553,7 +14659,9 @@
       <c r="H278" t="n">
         <v>8</v>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="n">
+        <v>7</v>
+      </c>
       <c r="J278" t="n">
         <v>24</v>
       </c>
@@ -13588,7 +14696,9 @@
       <c r="B279" t="n">
         <v>0.247</v>
       </c>
-      <c r="C279" t="inlineStr"/>
+      <c r="C279" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D279" t="n">
         <v>42</v>
       </c>
@@ -13600,7 +14710,9 @@
       <c r="H279" t="n">
         <v>8</v>
       </c>
-      <c r="I279" t="inlineStr"/>
+      <c r="I279" t="n">
+        <v>6</v>
+      </c>
       <c r="J279" t="n">
         <v>40</v>
       </c>
@@ -13635,7 +14747,9 @@
       <c r="B280" t="n">
         <v>0.24</v>
       </c>
-      <c r="C280" t="inlineStr"/>
+      <c r="C280" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D280" t="n">
         <v>43</v>
       </c>
@@ -13647,7 +14761,9 @@
       <c r="H280" t="n">
         <v>7</v>
       </c>
-      <c r="I280" t="inlineStr"/>
+      <c r="I280" t="n">
+        <v>6</v>
+      </c>
       <c r="J280" t="n">
         <v>32</v>
       </c>
@@ -13682,7 +14798,9 @@
       <c r="B281" t="n">
         <v>0.244</v>
       </c>
-      <c r="C281" t="inlineStr"/>
+      <c r="C281" t="n">
+        <v>0.246</v>
+      </c>
       <c r="D281" t="n">
         <v>49</v>
       </c>
@@ -13694,7 +14812,9 @@
       <c r="H281" t="n">
         <v>7</v>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="n">
+        <v>7</v>
+      </c>
       <c r="J281" t="n">
         <v>35</v>
       </c>
@@ -13729,7 +14849,9 @@
       <c r="B282" t="n">
         <v>0.191</v>
       </c>
-      <c r="C282" t="inlineStr"/>
+      <c r="C282" t="n">
+        <v>0.196</v>
+      </c>
       <c r="D282" t="n">
         <v>31</v>
       </c>
@@ -13741,7 +14863,9 @@
       <c r="H282" t="n">
         <v>7</v>
       </c>
-      <c r="I282" t="inlineStr"/>
+      <c r="I282" t="n">
+        <v>6</v>
+      </c>
       <c r="J282" t="n">
         <v>30</v>
       </c>
@@ -13776,7 +14900,9 @@
       <c r="B283" t="n">
         <v>0.209</v>
       </c>
-      <c r="C283" t="inlineStr"/>
+      <c r="C283" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D283" t="n">
         <v>48</v>
       </c>
@@ -13788,7 +14914,9 @@
       <c r="H283" t="n">
         <v>7</v>
       </c>
-      <c r="I283" t="inlineStr"/>
+      <c r="I283" t="n">
+        <v>6</v>
+      </c>
       <c r="J283" t="n">
         <v>28</v>
       </c>
@@ -13823,7 +14951,9 @@
       <c r="B284" t="n">
         <v>0.249</v>
       </c>
-      <c r="C284" t="inlineStr"/>
+      <c r="C284" t="n">
+        <v>0.219</v>
+      </c>
       <c r="D284" t="n">
         <v>20</v>
       </c>
@@ -13835,7 +14965,9 @@
       <c r="H284" t="n">
         <v>7</v>
       </c>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="n">
+        <v>7</v>
+      </c>
       <c r="J284" t="n">
         <v>28</v>
       </c>
@@ -13870,7 +15002,9 @@
       <c r="B285" t="n">
         <v>0.271</v>
       </c>
-      <c r="C285" t="inlineStr"/>
+      <c r="C285" t="n">
+        <v>0.238</v>
+      </c>
       <c r="D285" t="n">
         <v>52</v>
       </c>
@@ -13882,7 +15016,9 @@
       <c r="H285" t="n">
         <v>7</v>
       </c>
-      <c r="I285" t="inlineStr"/>
+      <c r="I285" t="n">
+        <v>7</v>
+      </c>
       <c r="J285" t="n">
         <v>44</v>
       </c>
@@ -13917,7 +15053,9 @@
       <c r="B286" t="n">
         <v>0.235</v>
       </c>
-      <c r="C286" t="inlineStr"/>
+      <c r="C286" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D286" t="n">
         <v>26</v>
       </c>
@@ -13929,7 +15067,9 @@
       <c r="H286" t="n">
         <v>7</v>
       </c>
-      <c r="I286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>8</v>
+      </c>
       <c r="J286" t="n">
         <v>25</v>
       </c>
@@ -13964,7 +15104,9 @@
       <c r="B287" t="n">
         <v>0.273</v>
       </c>
-      <c r="C287" t="inlineStr"/>
+      <c r="C287" t="n">
+        <v>0.281</v>
+      </c>
       <c r="D287" t="n">
         <v>65</v>
       </c>
@@ -13976,7 +15118,9 @@
       <c r="H287" t="n">
         <v>7</v>
       </c>
-      <c r="I287" t="inlineStr"/>
+      <c r="I287" t="n">
+        <v>6</v>
+      </c>
       <c r="J287" t="n">
         <v>47</v>
       </c>
@@ -14011,7 +15155,9 @@
       <c r="B288" t="n">
         <v>0.216</v>
       </c>
-      <c r="C288" t="inlineStr"/>
+      <c r="C288" t="n">
+        <v>0.195</v>
+      </c>
       <c r="D288" t="n">
         <v>32</v>
       </c>
@@ -14023,7 +15169,9 @@
       <c r="H288" t="n">
         <v>7</v>
       </c>
-      <c r="I288" t="inlineStr"/>
+      <c r="I288" t="n">
+        <v>7</v>
+      </c>
       <c r="J288" t="n">
         <v>25</v>
       </c>
@@ -14058,7 +15206,9 @@
       <c r="B289" t="n">
         <v>0.26</v>
       </c>
-      <c r="C289" t="inlineStr"/>
+      <c r="C289" t="n">
+        <v>0.27</v>
+      </c>
       <c r="D289" t="n">
         <v>36</v>
       </c>
@@ -14070,7 +15220,9 @@
       <c r="H289" t="n">
         <v>7</v>
       </c>
-      <c r="I289" t="inlineStr"/>
+      <c r="I289" t="n">
+        <v>7</v>
+      </c>
       <c r="J289" t="n">
         <v>43</v>
       </c>
@@ -14105,7 +15257,9 @@
       <c r="B290" t="n">
         <v>0.224</v>
       </c>
-      <c r="C290" t="inlineStr"/>
+      <c r="C290" t="n">
+        <v>0.211</v>
+      </c>
       <c r="D290" t="n">
         <v>34</v>
       </c>
@@ -14117,7 +15271,9 @@
       <c r="H290" t="n">
         <v>7</v>
       </c>
-      <c r="I290" t="inlineStr"/>
+      <c r="I290" t="n">
+        <v>9</v>
+      </c>
       <c r="J290" t="n">
         <v>32</v>
       </c>
@@ -14152,7 +15308,9 @@
       <c r="B291" t="n">
         <v>0.23</v>
       </c>
-      <c r="C291" t="inlineStr"/>
+      <c r="C291" t="n">
+        <v>0.187</v>
+      </c>
       <c r="D291" t="n">
         <v>22</v>
       </c>
@@ -14164,7 +15322,9 @@
       <c r="H291" t="n">
         <v>7</v>
       </c>
-      <c r="I291" t="inlineStr"/>
+      <c r="I291" t="n">
+        <v>5</v>
+      </c>
       <c r="J291" t="n">
         <v>22</v>
       </c>
@@ -14199,7 +15359,9 @@
       <c r="B292" t="n">
         <v>0.221</v>
       </c>
-      <c r="C292" t="inlineStr"/>
+      <c r="C292" t="n">
+        <v>0.228</v>
+      </c>
       <c r="D292" t="n">
         <v>25</v>
       </c>
@@ -14211,7 +15373,9 @@
       <c r="H292" t="n">
         <v>6</v>
       </c>
-      <c r="I292" t="inlineStr"/>
+      <c r="I292" t="n">
+        <v>6</v>
+      </c>
       <c r="J292" t="n">
         <v>27</v>
       </c>
@@ -14246,7 +15410,9 @@
       <c r="B293" t="n">
         <v>0.256</v>
       </c>
-      <c r="C293" t="inlineStr"/>
+      <c r="C293" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D293" t="n">
         <v>39</v>
       </c>
@@ -14258,7 +15424,9 @@
       <c r="H293" t="n">
         <v>6</v>
       </c>
-      <c r="I293" t="inlineStr"/>
+      <c r="I293" t="n">
+        <v>4</v>
+      </c>
       <c r="J293" t="n">
         <v>27</v>
       </c>
@@ -14293,7 +15461,9 @@
       <c r="B294" t="n">
         <v>0.26</v>
       </c>
-      <c r="C294" t="inlineStr"/>
+      <c r="C294" t="n">
+        <v>0.264</v>
+      </c>
       <c r="D294" t="n">
         <v>48</v>
       </c>
@@ -14305,7 +15475,9 @@
       <c r="H294" t="n">
         <v>6</v>
       </c>
-      <c r="I294" t="inlineStr"/>
+      <c r="I294" t="n">
+        <v>8</v>
+      </c>
       <c r="J294" t="n">
         <v>26</v>
       </c>
@@ -14340,7 +15512,9 @@
       <c r="B295" t="n">
         <v>0.269</v>
       </c>
-      <c r="C295" t="inlineStr"/>
+      <c r="C295" t="n">
+        <v>0.275</v>
+      </c>
       <c r="D295" t="n">
         <v>35</v>
       </c>
@@ -14352,7 +15526,9 @@
       <c r="H295" t="n">
         <v>6</v>
       </c>
-      <c r="I295" t="inlineStr"/>
+      <c r="I295" t="n">
+        <v>6</v>
+      </c>
       <c r="J295" t="n">
         <v>32</v>
       </c>
@@ -14387,7 +15563,9 @@
       <c r="B296" t="n">
         <v>0.277</v>
       </c>
-      <c r="C296" t="inlineStr"/>
+      <c r="C296" t="n">
+        <v>0.28</v>
+      </c>
       <c r="D296" t="n">
         <v>44</v>
       </c>
@@ -14399,7 +15577,9 @@
       <c r="H296" t="n">
         <v>6</v>
       </c>
-      <c r="I296" t="inlineStr"/>
+      <c r="I296" t="n">
+        <v>7</v>
+      </c>
       <c r="J296" t="n">
         <v>43</v>
       </c>
@@ -14434,7 +15614,9 @@
       <c r="B297" t="n">
         <v>0.25</v>
       </c>
-      <c r="C297" t="inlineStr"/>
+      <c r="C297" t="n">
+        <v>0.256</v>
+      </c>
       <c r="D297" t="n">
         <v>40</v>
       </c>
@@ -14446,7 +15628,9 @@
       <c r="H297" t="n">
         <v>6</v>
       </c>
-      <c r="I297" t="inlineStr"/>
+      <c r="I297" t="n">
+        <v>7</v>
+      </c>
       <c r="J297" t="n">
         <v>30</v>
       </c>
@@ -14481,7 +15665,9 @@
       <c r="B298" t="n">
         <v>0.265</v>
       </c>
-      <c r="C298" t="inlineStr"/>
+      <c r="C298" t="n">
+        <v>0.264</v>
+      </c>
       <c r="D298" t="n">
         <v>42</v>
       </c>
@@ -14493,7 +15679,9 @@
       <c r="H298" t="n">
         <v>6</v>
       </c>
-      <c r="I298" t="inlineStr"/>
+      <c r="I298" t="n">
+        <v>6</v>
+      </c>
       <c r="J298" t="n">
         <v>38</v>
       </c>
@@ -14528,7 +15716,9 @@
       <c r="B299" t="n">
         <v>0.271</v>
       </c>
-      <c r="C299" t="inlineStr"/>
+      <c r="C299" t="n">
+        <v>0.241</v>
+      </c>
       <c r="D299" t="n">
         <v>44</v>
       </c>
@@ -14540,7 +15730,9 @@
       <c r="H299" t="n">
         <v>6</v>
       </c>
-      <c r="I299" t="inlineStr"/>
+      <c r="I299" t="n">
+        <v>6</v>
+      </c>
       <c r="J299" t="n">
         <v>27</v>
       </c>
@@ -14575,7 +15767,9 @@
       <c r="B300" t="n">
         <v>0.179</v>
       </c>
-      <c r="C300" t="inlineStr"/>
+      <c r="C300" t="n">
+        <v>0.173</v>
+      </c>
       <c r="D300" t="n">
         <v>38</v>
       </c>
@@ -14587,7 +15781,9 @@
       <c r="H300" t="n">
         <v>6</v>
       </c>
-      <c r="I300" t="inlineStr"/>
+      <c r="I300" t="n">
+        <v>6</v>
+      </c>
       <c r="J300" t="n">
         <v>21</v>
       </c>
@@ -14622,7 +15818,9 @@
       <c r="B301" t="n">
         <v>0.241</v>
       </c>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="n">
+        <v>0.226</v>
+      </c>
       <c r="D301" t="n">
         <v>37</v>
       </c>
@@ -14634,7 +15832,9 @@
       <c r="H301" t="n">
         <v>6</v>
       </c>
-      <c r="I301" t="inlineStr"/>
+      <c r="I301" t="n">
+        <v>7</v>
+      </c>
       <c r="J301" t="n">
         <v>42</v>
       </c>
@@ -14669,7 +15869,9 @@
       <c r="B302" t="n">
         <v>0.234</v>
       </c>
-      <c r="C302" t="inlineStr"/>
+      <c r="C302" t="n">
+        <v>0.212</v>
+      </c>
       <c r="D302" t="n">
         <v>32</v>
       </c>
@@ -14681,7 +15883,9 @@
       <c r="H302" t="n">
         <v>6</v>
       </c>
-      <c r="I302" t="inlineStr"/>
+      <c r="I302" t="n">
+        <v>4</v>
+      </c>
       <c r="J302" t="n">
         <v>22</v>
       </c>
@@ -14716,7 +15920,9 @@
       <c r="B303" t="n">
         <v>0.25</v>
       </c>
-      <c r="C303" t="inlineStr"/>
+      <c r="C303" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D303" t="n">
         <v>30</v>
       </c>
@@ -14728,7 +15934,9 @@
       <c r="H303" t="n">
         <v>5</v>
       </c>
-      <c r="I303" t="inlineStr"/>
+      <c r="I303" t="n">
+        <v>5</v>
+      </c>
       <c r="J303" t="n">
         <v>28</v>
       </c>
@@ -14763,7 +15971,9 @@
       <c r="B304" t="n">
         <v>0.231</v>
       </c>
-      <c r="C304" t="inlineStr"/>
+      <c r="C304" t="n">
+        <v>0.195</v>
+      </c>
       <c r="D304" t="n">
         <v>29</v>
       </c>
@@ -14775,7 +15985,9 @@
       <c r="H304" t="n">
         <v>5</v>
       </c>
-      <c r="I304" t="inlineStr"/>
+      <c r="I304" t="n">
+        <v>5</v>
+      </c>
       <c r="J304" t="n">
         <v>26</v>
       </c>
@@ -14810,7 +16022,9 @@
       <c r="B305" t="n">
         <v>0.264</v>
       </c>
-      <c r="C305" t="inlineStr"/>
+      <c r="C305" t="n">
+        <v>0.264</v>
+      </c>
       <c r="D305" t="n">
         <v>44</v>
       </c>
@@ -14822,7 +16036,9 @@
       <c r="H305" t="n">
         <v>5</v>
       </c>
-      <c r="I305" t="inlineStr"/>
+      <c r="I305" t="n">
+        <v>6</v>
+      </c>
       <c r="J305" t="n">
         <v>35</v>
       </c>
@@ -14857,7 +16073,9 @@
       <c r="B306" t="n">
         <v>0.225</v>
       </c>
-      <c r="C306" t="inlineStr"/>
+      <c r="C306" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D306" t="n">
         <v>30</v>
       </c>
@@ -14869,7 +16087,9 @@
       <c r="H306" t="n">
         <v>5</v>
       </c>
-      <c r="I306" t="inlineStr"/>
+      <c r="I306" t="n">
+        <v>4</v>
+      </c>
       <c r="J306" t="n">
         <v>21</v>
       </c>
@@ -14904,7 +16124,9 @@
       <c r="B307" t="n">
         <v>0.221</v>
       </c>
-      <c r="C307" t="inlineStr"/>
+      <c r="C307" t="n">
+        <v>0.231</v>
+      </c>
       <c r="D307" t="n">
         <v>28</v>
       </c>
@@ -14916,7 +16138,9 @@
       <c r="H307" t="n">
         <v>5</v>
       </c>
-      <c r="I307" t="inlineStr"/>
+      <c r="I307" t="n">
+        <v>5</v>
+      </c>
       <c r="J307" t="n">
         <v>22</v>
       </c>
@@ -14951,7 +16175,9 @@
       <c r="B308" t="n">
         <v>0.23</v>
       </c>
-      <c r="C308" t="inlineStr"/>
+      <c r="C308" t="n">
+        <v>0.233</v>
+      </c>
       <c r="D308" t="n">
         <v>41</v>
       </c>
@@ -14963,7 +16189,9 @@
       <c r="H308" t="n">
         <v>5</v>
       </c>
-      <c r="I308" t="inlineStr"/>
+      <c r="I308" t="n">
+        <v>5</v>
+      </c>
       <c r="J308" t="n">
         <v>25</v>
       </c>
@@ -14998,7 +16226,9 @@
       <c r="B309" t="n">
         <v>0.221</v>
       </c>
-      <c r="C309" t="inlineStr"/>
+      <c r="C309" t="n">
+        <v>0.223</v>
+      </c>
       <c r="D309" t="n">
         <v>32</v>
       </c>
@@ -15010,7 +16240,9 @@
       <c r="H309" t="n">
         <v>5</v>
       </c>
-      <c r="I309" t="inlineStr"/>
+      <c r="I309" t="n">
+        <v>6</v>
+      </c>
       <c r="J309" t="n">
         <v>26</v>
       </c>
@@ -15045,7 +16277,9 @@
       <c r="B310" t="n">
         <v>0.222</v>
       </c>
-      <c r="C310" t="inlineStr"/>
+      <c r="C310" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D310" t="n">
         <v>17</v>
       </c>
@@ -15057,7 +16291,9 @@
       <c r="H310" t="n">
         <v>5</v>
       </c>
-      <c r="I310" t="inlineStr"/>
+      <c r="I310" t="n">
+        <v>4</v>
+      </c>
       <c r="J310" t="n">
         <v>21</v>
       </c>
@@ -15092,7 +16328,9 @@
       <c r="B311" t="n">
         <v>0.268</v>
       </c>
-      <c r="C311" t="inlineStr"/>
+      <c r="C311" t="n">
+        <v>0.247</v>
+      </c>
       <c r="D311" t="n">
         <v>40</v>
       </c>
@@ -15104,7 +16342,9 @@
       <c r="H311" t="n">
         <v>5</v>
       </c>
-      <c r="I311" t="inlineStr"/>
+      <c r="I311" t="n">
+        <v>5</v>
+      </c>
       <c r="J311" t="n">
         <v>31</v>
       </c>
@@ -15139,7 +16379,9 @@
       <c r="B312" t="n">
         <v>0.248</v>
       </c>
-      <c r="C312" t="inlineStr"/>
+      <c r="C312" t="n">
+        <v>0.218</v>
+      </c>
       <c r="D312" t="n">
         <v>25</v>
       </c>
@@ -15151,7 +16393,9 @@
       <c r="H312" t="n">
         <v>4</v>
       </c>
-      <c r="I312" t="inlineStr"/>
+      <c r="I312" t="n">
+        <v>3</v>
+      </c>
       <c r="J312" t="n">
         <v>25</v>
       </c>
@@ -15186,7 +16430,9 @@
       <c r="B313" t="n">
         <v>0.24</v>
       </c>
-      <c r="C313" t="inlineStr"/>
+      <c r="C313" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D313" t="n">
         <v>20</v>
       </c>
@@ -15198,7 +16444,9 @@
       <c r="H313" t="n">
         <v>4</v>
       </c>
-      <c r="I313" t="inlineStr"/>
+      <c r="I313" t="n">
+        <v>3</v>
+      </c>
       <c r="J313" t="n">
         <v>20</v>
       </c>
@@ -15233,7 +16481,9 @@
       <c r="B314" t="n">
         <v>0.21</v>
       </c>
-      <c r="C314" t="inlineStr"/>
+      <c r="C314" t="n">
+        <v>0.218</v>
+      </c>
       <c r="D314" t="n">
         <v>17</v>
       </c>
@@ -15245,7 +16495,9 @@
       <c r="H314" t="n">
         <v>4</v>
       </c>
-      <c r="I314" t="inlineStr"/>
+      <c r="I314" t="n">
+        <v>4</v>
+      </c>
       <c r="J314" t="n">
         <v>18</v>
       </c>
@@ -15280,7 +16532,9 @@
       <c r="B315" t="n">
         <v>0.262</v>
       </c>
-      <c r="C315" t="inlineStr"/>
+      <c r="C315" t="n">
+        <v>0.247</v>
+      </c>
       <c r="D315" t="n">
         <v>30</v>
       </c>
@@ -15292,7 +16546,9 @@
       <c r="H315" t="n">
         <v>4</v>
       </c>
-      <c r="I315" t="inlineStr"/>
+      <c r="I315" t="n">
+        <v>3</v>
+      </c>
       <c r="J315" t="n">
         <v>25</v>
       </c>
@@ -15327,7 +16583,9 @@
       <c r="B316" t="n">
         <v>0.255</v>
       </c>
-      <c r="C316" t="inlineStr"/>
+      <c r="C316" t="n">
+        <v>0.234</v>
+      </c>
       <c r="D316" t="n">
         <v>36</v>
       </c>
@@ -15339,7 +16597,9 @@
       <c r="H316" t="n">
         <v>4</v>
       </c>
-      <c r="I316" t="inlineStr"/>
+      <c r="I316" t="n">
+        <v>4</v>
+      </c>
       <c r="J316" t="n">
         <v>26</v>
       </c>
@@ -15374,7 +16634,9 @@
       <c r="B317" t="n">
         <v>0.261</v>
       </c>
-      <c r="C317" t="inlineStr"/>
+      <c r="C317" t="n">
+        <v>0.266</v>
+      </c>
       <c r="D317" t="n">
         <v>52</v>
       </c>
@@ -15386,7 +16648,9 @@
       <c r="H317" t="n">
         <v>4</v>
       </c>
-      <c r="I317" t="inlineStr"/>
+      <c r="I317" t="n">
+        <v>4</v>
+      </c>
       <c r="J317" t="n">
         <v>32</v>
       </c>
@@ -15421,7 +16685,9 @@
       <c r="B318" t="n">
         <v>0.281</v>
       </c>
-      <c r="C318" t="inlineStr"/>
+      <c r="C318" t="n">
+        <v>0.263</v>
+      </c>
       <c r="D318" t="n">
         <v>39</v>
       </c>
@@ -15433,7 +16699,9 @@
       <c r="H318" t="n">
         <v>4</v>
       </c>
-      <c r="I318" t="inlineStr"/>
+      <c r="I318" t="n">
+        <v>2</v>
+      </c>
       <c r="J318" t="n">
         <v>27</v>
       </c>
@@ -15468,7 +16736,9 @@
       <c r="B319" t="n">
         <v>0.243</v>
       </c>
-      <c r="C319" t="inlineStr"/>
+      <c r="C319" t="n">
+        <v>0.23</v>
+      </c>
       <c r="D319" t="n">
         <v>40</v>
       </c>
@@ -15480,7 +16750,9 @@
       <c r="H319" t="n">
         <v>4</v>
       </c>
-      <c r="I319" t="inlineStr"/>
+      <c r="I319" t="n">
+        <v>3</v>
+      </c>
       <c r="J319" t="n">
         <v>23</v>
       </c>
@@ -15515,7 +16787,9 @@
       <c r="B320" t="n">
         <v>0.258</v>
       </c>
-      <c r="C320" t="inlineStr"/>
+      <c r="C320" t="n">
+        <v>0.264</v>
+      </c>
       <c r="D320" t="n">
         <v>35</v>
       </c>
@@ -15527,7 +16801,9 @@
       <c r="H320" t="n">
         <v>4</v>
       </c>
-      <c r="I320" t="inlineStr"/>
+      <c r="I320" t="n">
+        <v>3</v>
+      </c>
       <c r="J320" t="n">
         <v>31</v>
       </c>
@@ -15562,7 +16838,9 @@
       <c r="B321" t="n">
         <v>0.229</v>
       </c>
-      <c r="C321" t="inlineStr"/>
+      <c r="C321" t="n">
+        <v>0.21</v>
+      </c>
       <c r="D321" t="n">
         <v>32</v>
       </c>
@@ -15574,7 +16852,9 @@
       <c r="H321" t="n">
         <v>4</v>
       </c>
-      <c r="I321" t="inlineStr"/>
+      <c r="I321" t="n">
+        <v>5</v>
+      </c>
       <c r="J321" t="n">
         <v>28</v>
       </c>
@@ -15609,7 +16889,9 @@
       <c r="B322" t="n">
         <v>0.235</v>
       </c>
-      <c r="C322" t="inlineStr"/>
+      <c r="C322" t="n">
+        <v>0.258</v>
+      </c>
       <c r="D322" t="n">
         <v>26</v>
       </c>
@@ -15621,7 +16903,9 @@
       <c r="H322" t="n">
         <v>4</v>
       </c>
-      <c r="I322" t="inlineStr"/>
+      <c r="I322" t="n">
+        <v>5</v>
+      </c>
       <c r="J322" t="n">
         <v>30</v>
       </c>
@@ -15656,7 +16940,9 @@
       <c r="B323" t="n">
         <v>0.276</v>
       </c>
-      <c r="C323" t="inlineStr"/>
+      <c r="C323" t="n">
+        <v>0.286</v>
+      </c>
       <c r="D323" t="n">
         <v>44</v>
       </c>
@@ -15668,7 +16954,9 @@
       <c r="H323" t="n">
         <v>4</v>
       </c>
-      <c r="I323" t="inlineStr"/>
+      <c r="I323" t="n">
+        <v>6</v>
+      </c>
       <c r="J323" t="n">
         <v>42</v>
       </c>
@@ -15703,7 +16991,9 @@
       <c r="B324" t="n">
         <v>0.172</v>
       </c>
-      <c r="C324" t="inlineStr"/>
+      <c r="C324" t="n">
+        <v>0.198</v>
+      </c>
       <c r="D324" t="n">
         <v>21</v>
       </c>
@@ -15715,7 +17005,9 @@
       <c r="H324" t="n">
         <v>4</v>
       </c>
-      <c r="I324" t="inlineStr"/>
+      <c r="I324" t="n">
+        <v>4</v>
+      </c>
       <c r="J324" t="n">
         <v>11</v>
       </c>
@@ -15750,7 +17042,9 @@
       <c r="B325" t="n">
         <v>0.288</v>
       </c>
-      <c r="C325" t="inlineStr"/>
+      <c r="C325" t="n">
+        <v>0.314</v>
+      </c>
       <c r="D325" t="n">
         <v>63</v>
       </c>
@@ -15762,7 +17056,9 @@
       <c r="H325" t="n">
         <v>3</v>
       </c>
-      <c r="I325" t="inlineStr"/>
+      <c r="I325" t="n">
+        <v>1</v>
+      </c>
       <c r="J325" t="n">
         <v>30</v>
       </c>
@@ -15797,7 +17093,9 @@
       <c r="B326" t="n">
         <v>0.234</v>
       </c>
-      <c r="C326" t="inlineStr"/>
+      <c r="C326" t="n">
+        <v>0.225</v>
+      </c>
       <c r="D326" t="n">
         <v>34</v>
       </c>
@@ -15809,7 +17107,9 @@
       <c r="H326" t="n">
         <v>3</v>
       </c>
-      <c r="I326" t="inlineStr"/>
+      <c r="I326" t="n">
+        <v>3</v>
+      </c>
       <c r="J326" t="n">
         <v>23</v>
       </c>
@@ -15844,7 +17144,9 @@
       <c r="B327" t="n">
         <v>0.23</v>
       </c>
-      <c r="C327" t="inlineStr"/>
+      <c r="C327" t="n">
+        <v>0.223</v>
+      </c>
       <c r="D327" t="n">
         <v>55</v>
       </c>
@@ -15856,7 +17158,9 @@
       <c r="H327" t="n">
         <v>3</v>
       </c>
-      <c r="I327" t="inlineStr"/>
+      <c r="I327" t="n">
+        <v>2</v>
+      </c>
       <c r="J327" t="n">
         <v>22</v>
       </c>
@@ -15891,7 +17195,9 @@
       <c r="B328" t="n">
         <v>0.245</v>
       </c>
-      <c r="C328" t="inlineStr"/>
+      <c r="C328" t="n">
+        <v>0.247</v>
+      </c>
       <c r="D328" t="n">
         <v>35</v>
       </c>
@@ -15903,7 +17209,9 @@
       <c r="H328" t="n">
         <v>3</v>
       </c>
-      <c r="I328" t="inlineStr"/>
+      <c r="I328" t="n">
+        <v>3</v>
+      </c>
       <c r="J328" t="n">
         <v>30</v>
       </c>
@@ -15938,7 +17246,9 @@
       <c r="B329" t="n">
         <v>0.3</v>
       </c>
-      <c r="C329" t="inlineStr"/>
+      <c r="C329" t="n">
+        <v>0.318</v>
+      </c>
       <c r="D329" t="n">
         <v>71</v>
       </c>
@@ -15950,7 +17260,9 @@
       <c r="H329" t="n">
         <v>3</v>
       </c>
-      <c r="I329" t="inlineStr"/>
+      <c r="I329" t="n">
+        <v>3</v>
+      </c>
       <c r="J329" t="n">
         <v>41</v>
       </c>
@@ -15985,7 +17297,9 @@
       <c r="B330" t="n">
         <v>0.246</v>
       </c>
-      <c r="C330" t="inlineStr"/>
+      <c r="C330" t="n">
+        <v>0.243</v>
+      </c>
       <c r="D330" t="n">
         <v>34</v>
       </c>
@@ -15997,7 +17311,9 @@
       <c r="H330" t="n">
         <v>3</v>
       </c>
-      <c r="I330" t="inlineStr"/>
+      <c r="I330" t="n">
+        <v>3</v>
+      </c>
       <c r="J330" t="n">
         <v>24</v>
       </c>
@@ -16032,7 +17348,9 @@
       <c r="B331" t="n">
         <v>0.25</v>
       </c>
-      <c r="C331" t="inlineStr"/>
+      <c r="C331" t="n">
+        <v>0.208</v>
+      </c>
       <c r="D331" t="n">
         <v>35</v>
       </c>
@@ -16044,7 +17362,9 @@
       <c r="H331" t="n">
         <v>3</v>
       </c>
-      <c r="I331" t="inlineStr"/>
+      <c r="I331" t="n">
+        <v>1</v>
+      </c>
       <c r="J331" t="n">
         <v>17</v>
       </c>
@@ -16079,7 +17399,9 @@
       <c r="B332" t="n">
         <v>0.257</v>
       </c>
-      <c r="C332" t="inlineStr"/>
+      <c r="C332" t="n">
+        <v>0.232</v>
+      </c>
       <c r="D332" t="n">
         <v>24</v>
       </c>
@@ -16091,7 +17413,9 @@
       <c r="H332" t="n">
         <v>3</v>
       </c>
-      <c r="I332" t="inlineStr"/>
+      <c r="I332" t="n">
+        <v>3</v>
+      </c>
       <c r="J332" t="n">
         <v>21</v>
       </c>
@@ -16126,7 +17450,9 @@
       <c r="B333" t="n">
         <v>0.257</v>
       </c>
-      <c r="C333" t="inlineStr"/>
+      <c r="C333" t="n">
+        <v>0.247</v>
+      </c>
       <c r="D333" t="n">
         <v>31</v>
       </c>
@@ -16138,7 +17464,9 @@
       <c r="H333" t="n">
         <v>3</v>
       </c>
-      <c r="I333" t="inlineStr"/>
+      <c r="I333" t="n">
+        <v>2</v>
+      </c>
       <c r="J333" t="n">
         <v>22</v>
       </c>
@@ -16173,7 +17501,9 @@
       <c r="B334" t="n">
         <v>0.223</v>
       </c>
-      <c r="C334" t="inlineStr"/>
+      <c r="C334" t="n">
+        <v>0.208</v>
+      </c>
       <c r="D334" t="n">
         <v>14</v>
       </c>
@@ -16185,7 +17515,9 @@
       <c r="H334" t="n">
         <v>3</v>
       </c>
-      <c r="I334" t="inlineStr"/>
+      <c r="I334" t="n">
+        <v>2</v>
+      </c>
       <c r="J334" t="n">
         <v>17</v>
       </c>
@@ -16220,7 +17552,9 @@
       <c r="B335" t="n">
         <v>0.225</v>
       </c>
-      <c r="C335" t="inlineStr"/>
+      <c r="C335" t="n">
+        <v>0.196</v>
+      </c>
       <c r="D335" t="n">
         <v>35</v>
       </c>
@@ -16232,7 +17566,9 @@
       <c r="H335" t="n">
         <v>2</v>
       </c>
-      <c r="I335" t="inlineStr"/>
+      <c r="I335" t="n">
+        <v>2</v>
+      </c>
       <c r="J335" t="n">
         <v>25</v>
       </c>
@@ -16267,7 +17603,9 @@
       <c r="B336" t="n">
         <v>0.249</v>
       </c>
-      <c r="C336" t="inlineStr"/>
+      <c r="C336" t="n">
+        <v>0.271</v>
+      </c>
       <c r="D336" t="n">
         <v>32</v>
       </c>
@@ -16279,7 +17617,9 @@
       <c r="H336" t="n">
         <v>2</v>
       </c>
-      <c r="I336" t="inlineStr"/>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
       <c r="J336" t="n">
         <v>21</v>
       </c>
@@ -16314,7 +17654,9 @@
       <c r="B337" t="n">
         <v>0.271</v>
       </c>
-      <c r="C337" t="inlineStr"/>
+      <c r="C337" t="n">
+        <v>0.273</v>
+      </c>
       <c r="D337" t="n">
         <v>53</v>
       </c>
@@ -16326,7 +17668,9 @@
       <c r="H337" t="n">
         <v>2</v>
       </c>
-      <c r="I337" t="inlineStr"/>
+      <c r="I337" t="n">
+        <v>2</v>
+      </c>
       <c r="J337" t="n">
         <v>25</v>
       </c>
@@ -16361,7 +17705,9 @@
       <c r="B338" t="n">
         <v>0.235</v>
       </c>
-      <c r="C338" t="inlineStr"/>
+      <c r="C338" t="n">
+        <v>0.252</v>
+      </c>
       <c r="D338" t="n">
         <v>46</v>
       </c>
@@ -16373,7 +17719,9 @@
       <c r="H338" t="n">
         <v>2</v>
       </c>
-      <c r="I338" t="inlineStr"/>
+      <c r="I338" t="n">
+        <v>3</v>
+      </c>
       <c r="J338" t="n">
         <v>22</v>
       </c>
@@ -16408,7 +17756,9 @@
       <c r="B339" t="n">
         <v>0.241</v>
       </c>
-      <c r="C339" t="inlineStr"/>
+      <c r="C339" t="n">
+        <v>0.247</v>
+      </c>
       <c r="D339" t="n">
         <v>24</v>
       </c>
@@ -16420,7 +17770,9 @@
       <c r="H339" t="n">
         <v>2</v>
       </c>
-      <c r="I339" t="inlineStr"/>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
       <c r="J339" t="n">
         <v>19</v>
       </c>
@@ -16455,7 +17807,9 @@
       <c r="B340" t="n">
         <v>0.237</v>
       </c>
-      <c r="C340" t="inlineStr"/>
+      <c r="C340" t="n">
+        <v>0.224</v>
+      </c>
       <c r="D340" t="n">
         <v>51</v>
       </c>
@@ -16467,7 +17821,9 @@
       <c r="H340" t="n">
         <v>2</v>
       </c>
-      <c r="I340" t="inlineStr"/>
+      <c r="I340" t="n">
+        <v>3</v>
+      </c>
       <c r="J340" t="n">
         <v>28</v>
       </c>
@@ -16502,7 +17858,9 @@
       <c r="B341" t="n">
         <v>0.247</v>
       </c>
-      <c r="C341" t="inlineStr"/>
+      <c r="C341" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D341" t="n">
         <v>24</v>
       </c>
@@ -16514,7 +17872,9 @@
       <c r="H341" t="n">
         <v>1</v>
       </c>
-      <c r="I341" t="inlineStr"/>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
       <c r="J341" t="n">
         <v>13</v>
       </c>
@@ -16549,7 +17909,9 @@
       <c r="B342" t="n">
         <v>0.318</v>
       </c>
-      <c r="C342" t="inlineStr"/>
+      <c r="C342" t="n">
+        <v>0.36</v>
+      </c>
       <c r="D342" t="n">
         <v>55</v>
       </c>
@@ -16561,7 +17923,9 @@
       <c r="H342" t="n">
         <v>1</v>
       </c>
-      <c r="I342" t="inlineStr"/>
+      <c r="I342" t="n">
+        <v>2</v>
+      </c>
       <c r="J342" t="n">
         <v>43</v>
       </c>
@@ -16596,7 +17960,9 @@
       <c r="B343" t="n">
         <v>0.222</v>
       </c>
-      <c r="C343" t="inlineStr"/>
+      <c r="C343" t="n">
+        <v>0.216</v>
+      </c>
       <c r="D343" t="n">
         <v>36</v>
       </c>
@@ -16608,7 +17974,9 @@
       <c r="H343" t="n">
         <v>1</v>
       </c>
-      <c r="I343" t="inlineStr"/>
+      <c r="I343" t="n">
+        <v>1</v>
+      </c>
       <c r="J343" t="n">
         <v>19</v>
       </c>
@@ -16643,7 +18011,9 @@
       <c r="B344" t="n">
         <v>0.29</v>
       </c>
-      <c r="C344" t="inlineStr"/>
+      <c r="C344" t="n">
+        <v>0.309</v>
+      </c>
       <c r="D344" t="n">
         <v>40</v>
       </c>
@@ -16655,7 +18025,9 @@
       <c r="H344" t="n">
         <v>0</v>
       </c>
-      <c r="I344" t="inlineStr"/>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
       <c r="J344" t="n">
         <v>26</v>
       </c>
@@ -16690,7 +18062,9 @@
       <c r="B345" t="n">
         <v>0.228</v>
       </c>
-      <c r="C345" t="inlineStr"/>
+      <c r="C345" t="n">
+        <v>0.261</v>
+      </c>
       <c r="D345" t="n">
         <v>11</v>
       </c>
@@ -16702,7 +18076,9 @@
       <c r="H345" t="n">
         <v>0</v>
       </c>
-      <c r="I345" t="inlineStr"/>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
       <c r="J345" t="n">
         <v>6</v>
       </c>
@@ -16737,7 +18113,9 @@
       <c r="B346" t="n">
         <v>0.22</v>
       </c>
-      <c r="C346" t="inlineStr"/>
+      <c r="C346" t="n">
+        <v>0.24</v>
+      </c>
       <c r="D346" t="n">
         <v>28</v>
       </c>
@@ -16749,7 +18127,9 @@
       <c r="H346" t="n">
         <v>0</v>
       </c>
-      <c r="I346" t="inlineStr"/>
+      <c r="I346" t="n">
+        <v>1</v>
+      </c>
       <c r="J346" t="n">
         <v>13</v>
       </c>
@@ -16784,7 +18164,9 @@
       <c r="B347" t="n">
         <v>0.31</v>
       </c>
-      <c r="C347" t="inlineStr"/>
+      <c r="C347" t="n">
+        <v>0.325</v>
+      </c>
       <c r="D347" t="n">
         <v>65</v>
       </c>
@@ -16796,7 +18178,9 @@
       <c r="H347" t="n">
         <v>0</v>
       </c>
-      <c r="I347" t="inlineStr"/>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
       <c r="J347" t="n">
         <v>20</v>
       </c>
@@ -16831,7 +18215,9 @@
       <c r="B348" t="n">
         <v>0.257</v>
       </c>
-      <c r="C348" t="inlineStr"/>
+      <c r="C348" t="n">
+        <v>0.251</v>
+      </c>
       <c r="D348" t="n">
         <v>44</v>
       </c>
@@ -16843,7 +18229,9 @@
       <c r="H348" t="n">
         <v>0</v>
       </c>
-      <c r="I348" t="inlineStr"/>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
       <c r="J348" t="n">
         <v>17</v>
       </c>
@@ -16878,7 +18266,9 @@
       <c r="B349" t="n">
         <v>0.227</v>
       </c>
-      <c r="C349" t="inlineStr"/>
+      <c r="C349" t="n">
+        <v>0.255</v>
+      </c>
       <c r="D349" t="n">
         <v>38</v>
       </c>
@@ -16890,7 +18280,9 @@
       <c r="H349" t="n">
         <v>0</v>
       </c>
-      <c r="I349" t="inlineStr"/>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
       <c r="J349" t="n">
         <v>16</v>
       </c>
@@ -31679,7 +33071,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-27 10:15</t>
+          <t>2026-03-27 15:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
